--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-11).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-11).xlsx
@@ -912,63 +912,66 @@
   </si>
   <si>
     <t>214
-127</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>R$ 1.293.701,63</t>
-  </si>
-  <si>
-    <t>R$ 9.307,21
-R$ 9.603,19</t>
-  </si>
-  <si>
-    <t>(5.9%)
-(2.9%)</t>
-  </si>
-  <si>
-    <t>99.8</t>
-  </si>
-  <si>
-    <t>(10.6%)</t>
-  </si>
-  <si>
-    <t>(3.0%)</t>
-  </si>
-  <si>
-    <t>(50.4%)</t>
-  </si>
-  <si>
-    <t>2.2%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>28.3</t>
-  </si>
-  <si>
-    <t>63.4%</t>
-  </si>
-  <si>
-    <t>12.9%</t>
-  </si>
-  <si>
-    <t>6.5</t>
-  </si>
-  <si>
-    <t>7.1</t>
-  </si>
-  <si>
-    <t>20.1</t>
-  </si>
-  <si>
-    <t>65.8%</t>
-  </si>
-  <si>
-    <t>-R$ 28.031,99</t>
+162</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>R$ 1.624.530,98</t>
+  </si>
+  <si>
+    <t>R$ 9.178,14
+R$ 9.506,28</t>
+  </si>
+  <si>
+    <t>(6.6%)
+(3.3%)</t>
+  </si>
+  <si>
+    <t>98.4</t>
+  </si>
+  <si>
+    <t>(11.7%)</t>
+  </si>
+  <si>
+    <t>(8.7%)</t>
+  </si>
+  <si>
+    <t>(52.9%)</t>
+  </si>
+  <si>
+    <t>2.7%</t>
+  </si>
+  <si>
+    <t>0.7%</t>
+  </si>
+  <si>
+    <t>29.1</t>
+  </si>
+  <si>
+    <t>61.7%</t>
+  </si>
+  <si>
+    <t>14.5%</t>
+  </si>
+  <si>
+    <t>6.6</t>
+  </si>
+  <si>
+    <t>7.7</t>
+  </si>
+  <si>
+    <t>14.3</t>
+  </si>
+  <si>
+    <t>20.8</t>
+  </si>
+  <si>
+    <t>64.1%</t>
+  </si>
+  <si>
+    <t>-R$ 40.199,49</t>
   </si>
   <si>
     <t>2.94</t>
@@ -1750,7 +1753,9 @@
       <c r="AB3" s="8">
         <v>3.5296471153846154</v>
       </c>
-      <c r="AC3" s="8"/>
+      <c r="AC3" s="8">
+        <v>10.903805999999999</v>
+      </c>
       <c r="AD3" s="8">
         <v>17.621254128440366</v>
       </c>
@@ -1879,7 +1884,9 @@
       <c r="AB4" s="8">
         <v>4.2510000000000003</v>
       </c>
-      <c r="AC4" s="8"/>
+      <c r="AC4" s="8">
+        <v>12.436500000000001</v>
+      </c>
       <c r="AD4" s="8">
         <v>17.674666999999999</v>
       </c>
@@ -2008,7 +2015,9 @@
       <c r="AB5" s="8">
         <v>7.6645837500000003</v>
       </c>
-      <c r="AC5" s="8"/>
+      <c r="AC5" s="8">
+        <v>10.966903</v>
+      </c>
       <c r="AD5" s="8">
         <v>16.851041250000002</v>
       </c>
@@ -2230,7 +2239,9 @@
       <c r="AB7" s="8">
         <v>2.584444</v>
       </c>
-      <c r="AC7" s="8"/>
+      <c r="AC7" s="8">
+        <v>11.910321</v>
+      </c>
       <c r="AD7" s="8">
         <v>18.747999999999998</v>
       </c>
@@ -2361,7 +2372,9 @@
       <c r="AB8" s="8">
         <v>3.6656612068965519</v>
       </c>
-      <c r="AC8" s="8"/>
+      <c r="AC8" s="8">
+        <v>14.781464</v>
+      </c>
       <c r="AD8" s="8">
         <v>21.727011206896549</v>
       </c>
@@ -2490,7 +2503,9 @@
       <c r="AB9" s="8">
         <v>4.6175824175824172</v>
       </c>
-      <c r="AC9" s="8"/>
+      <c r="AC9" s="8">
+        <v>9.9120830000000009</v>
+      </c>
       <c r="AD9" s="8">
         <v>15.479553608247421</v>
       </c>
@@ -2539,7 +2554,7 @@
         <v>19512</v>
       </c>
       <c r="B10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C10" s="4">
         <v>44</v>
@@ -2575,25 +2590,61 @@
       <c t="s" r="N10" s="4">
         <v>52</v>
       </c>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="7"/>
-      <c r="S10" s="6"/>
-      <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
-      <c r="V10" s="6"/>
-      <c r="W10" s="6"/>
-      <c r="X10" s="8"/>
-      <c r="Y10" s="6"/>
-      <c r="Z10" s="6"/>
-      <c r="AA10" s="8"/>
-      <c r="AB10" s="8"/>
-      <c r="AC10" s="8"/>
-      <c r="AD10" s="8"/>
-      <c r="AE10" s="6"/>
+      <c r="O10" s="5">
+        <v>10731.690000000001</v>
+      </c>
+      <c r="P10" s="5">
+        <v>10731.690000000001</v>
+      </c>
+      <c r="Q10" s="6">
+        <v>0.68363211920685663</v>
+      </c>
+      <c r="R10" s="7">
+        <v>99</v>
+      </c>
+      <c r="S10" s="6">
+        <v>0.546875</v>
+      </c>
+      <c r="T10" s="6">
+        <v>0.31089112711977329</v>
+      </c>
+      <c r="U10" s="6">
+        <v>0.0048992469965121986</v>
+      </c>
+      <c r="V10" s="6">
+        <v>0.020120269966799262</v>
+      </c>
+      <c r="W10" s="6">
+        <v>-0.0014056965864649462</v>
+      </c>
+      <c r="X10" s="8">
+        <v>22.702272727272724</v>
+      </c>
+      <c r="Y10" s="6">
+        <v>0.51515151515151514</v>
+      </c>
+      <c r="Z10" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="8">
+        <v>4.643027551020408</v>
+      </c>
+      <c r="AB10" s="8">
+        <v>3.0712121212121208</v>
+      </c>
+      <c r="AC10" s="8">
+        <v>8.0813129999999997</v>
+      </c>
+      <c r="AD10" s="8">
+        <v>15.023989393939393</v>
+      </c>
+      <c r="AE10" s="6">
+        <v>0.98484848484848486</v>
+      </c>
       <c r="AF10" s="9"/>
-      <c r="AG10" s="5"/>
+      <c r="AG10" s="5">
+        <v>-111.8</v>
+      </c>
       <c r="AH10" s="10">
         <v>5</v>
       </c>
@@ -2712,7 +2763,9 @@
       <c r="AB11" s="8">
         <v>5.5293253164556964</v>
       </c>
-      <c r="AC11" s="8"/>
+      <c r="AC11" s="8">
+        <v>9.9506320000000006</v>
+      </c>
       <c r="AD11" s="8">
         <v>15.885443037974683</v>
       </c>
@@ -2841,7 +2894,9 @@
       <c r="AB12" s="8">
         <v>6.1493766355140185</v>
       </c>
-      <c r="AC12" s="8"/>
+      <c r="AC12" s="8">
+        <v>11.255382000000001</v>
+      </c>
       <c r="AD12" s="8">
         <v>17.671020720720723</v>
       </c>
@@ -3099,7 +3154,9 @@
       <c r="AB14" s="8">
         <v>4.5032335820895524</v>
       </c>
-      <c r="AC14" s="8"/>
+      <c r="AC14" s="8">
+        <v>9.2139729999999993</v>
+      </c>
       <c r="AD14" s="8">
         <v>16.177860447761191</v>
       </c>
@@ -3228,7 +3285,9 @@
       <c r="AB15" s="8">
         <v>3.3840909090909093</v>
       </c>
-      <c r="AC15" s="8"/>
+      <c r="AC15" s="8">
+        <v>11.789861999999999</v>
+      </c>
       <c r="AD15" s="8">
         <v>18.698970224719101</v>
       </c>
@@ -3357,7 +3416,9 @@
       <c r="AB16" s="8">
         <v>28.463333333333331</v>
       </c>
-      <c r="AC16" s="8"/>
+      <c r="AC16" s="8">
+        <v>33.395555000000002</v>
+      </c>
       <c r="AD16" s="8">
         <v>40.295553333333338</v>
       </c>
@@ -3408,7 +3469,7 @@
         <v>19521</v>
       </c>
       <c r="B17" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C17" s="4">
         <v>44</v>
@@ -3444,10 +3505,16 @@
       <c t="s" r="N17" s="4">
         <v>52</v>
       </c>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
+      <c r="O17" s="5">
+        <v>0</v>
+      </c>
+      <c r="P17" s="5">
+        <v>0</v>
+      </c>
       <c r="Q17" s="6"/>
-      <c r="R17" s="7"/>
+      <c r="R17" s="7">
+        <v>0</v>
+      </c>
       <c r="S17" s="6"/>
       <c r="T17" s="6"/>
       <c r="U17" s="6"/>
@@ -3462,7 +3529,9 @@
       <c r="AD17" s="8"/>
       <c r="AE17" s="6"/>
       <c r="AF17" s="9"/>
-      <c r="AG17" s="5"/>
+      <c r="AG17" s="5">
+        <v>0</v>
+      </c>
       <c r="AH17" s="10">
         <v>5</v>
       </c>
@@ -3581,7 +3650,9 @@
       <c r="AB18" s="8">
         <v>6.7260609090909096</v>
       </c>
-      <c r="AC18" s="8"/>
+      <c r="AC18" s="8">
+        <v>10.838181000000001</v>
+      </c>
       <c r="AD18" s="8">
         <v>17.774848181818182</v>
       </c>
@@ -3710,7 +3781,9 @@
       <c r="AB19" s="8">
         <v>8.3244258620689653</v>
       </c>
-      <c r="AC19" s="8"/>
+      <c r="AC19" s="8">
+        <v>12.833182000000001</v>
+      </c>
       <c r="AD19" s="8">
         <v>19.589830508474577</v>
       </c>
@@ -3839,7 +3912,9 @@
       <c r="AB20" s="8">
         <v>5.5711864406779661</v>
       </c>
-      <c r="AC20" s="8"/>
+      <c r="AC20" s="8">
+        <v>11.531637</v>
+      </c>
       <c r="AD20" s="8">
         <v>18.47542372881356</v>
       </c>
@@ -3968,7 +4043,9 @@
       <c r="AB21" s="8">
         <v>3.1716671428571428</v>
       </c>
-      <c r="AC21" s="8"/>
+      <c r="AC21" s="8">
+        <v>6.2680939999999996</v>
+      </c>
       <c r="AD21" s="8">
         <v>12.228571428571428</v>
       </c>
@@ -4097,7 +4174,9 @@
       <c r="AB22" s="8">
         <v>5.5874481481481482</v>
       </c>
-      <c r="AC22" s="8"/>
+      <c r="AC22" s="8">
+        <v>11.482426999999999</v>
+      </c>
       <c r="AD22" s="8">
         <v>18.190762650602409</v>
       </c>
@@ -4226,7 +4305,9 @@
       <c r="AB23" s="8">
         <v>5.1704335616438355</v>
       </c>
-      <c r="AC23" s="8"/>
+      <c r="AC23" s="8">
+        <v>12.836086</v>
+      </c>
       <c r="AD23" s="8">
         <v>19.660472972972972</v>
       </c>
@@ -4450,7 +4531,9 @@
       <c r="AB25" s="8">
         <v>8.0071428571428562</v>
       </c>
-      <c r="AC25" s="8"/>
+      <c r="AC25" s="8">
+        <v>15.243955</v>
+      </c>
       <c r="AD25" s="8">
         <v>22.161538461538463</v>
       </c>
@@ -4579,7 +4662,9 @@
       <c r="AB26" s="8">
         <v>11.473767826086958</v>
       </c>
-      <c r="AC26" s="8"/>
+      <c r="AC26" s="8">
+        <v>20.163174000000001</v>
+      </c>
       <c r="AD26" s="8">
         <v>26.687994067796613</v>
       </c>
@@ -4708,7 +4793,9 @@
       <c r="AB27" s="8">
         <v>9.4882352941176471</v>
       </c>
-      <c r="AC27" s="8"/>
+      <c r="AC27" s="8">
+        <v>13.754593</v>
+      </c>
       <c r="AD27" s="8">
         <v>20.760909090909088</v>
       </c>
@@ -4759,7 +4846,7 @@
         <v>19546</v>
       </c>
       <c r="B28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C28" s="4">
         <v>44</v>
@@ -4795,25 +4882,61 @@
       <c t="s" r="N28" s="4">
         <v>52</v>
       </c>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="7"/>
-      <c r="S28" s="6"/>
-      <c r="T28" s="6"/>
-      <c r="U28" s="6"/>
-      <c r="V28" s="6"/>
-      <c r="W28" s="6"/>
-      <c r="X28" s="8"/>
-      <c r="Y28" s="6"/>
-      <c r="Z28" s="6"/>
-      <c r="AA28" s="8"/>
-      <c r="AB28" s="8"/>
-      <c r="AC28" s="8"/>
-      <c r="AD28" s="8"/>
-      <c r="AE28" s="6"/>
+      <c r="O28" s="5">
+        <v>8020.2700000000004</v>
+      </c>
+      <c r="P28" s="5">
+        <v>8020.2700000000004</v>
+      </c>
+      <c r="Q28" s="6">
+        <v>-0.13690562025556186</v>
+      </c>
+      <c r="R28" s="7">
+        <v>90</v>
+      </c>
+      <c r="S28" s="6">
+        <v>-0.090909090909090939</v>
+      </c>
+      <c r="T28" s="6">
+        <v>0.00023307195393671283</v>
+      </c>
+      <c r="U28" s="6">
+        <v>-0.31125519465055412</v>
+      </c>
+      <c r="V28" s="6">
+        <v>0.063891863989616299</v>
+      </c>
+      <c r="W28" s="6">
+        <v>0.056354711250369373</v>
+      </c>
+      <c r="X28" s="8">
+        <v>30.353488372093025</v>
+      </c>
+      <c r="Y28" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="Z28" s="6">
+        <v>0.11627906976744186</v>
+      </c>
+      <c r="AA28" s="8">
+        <v>2.9308988764044948</v>
+      </c>
+      <c r="AB28" s="8">
+        <v>11.816666666666666</v>
+      </c>
+      <c r="AC28" s="8">
+        <v>14.072222</v>
+      </c>
+      <c r="AD28" s="8">
+        <v>21.19222222222222</v>
+      </c>
+      <c r="AE28" s="6">
+        <v>0.60465116279069764</v>
+      </c>
       <c r="AF28" s="9"/>
-      <c r="AG28" s="5"/>
+      <c r="AG28" s="5">
+        <v>-1178.4400000000001</v>
+      </c>
       <c r="AH28" s="10">
         <v>2</v>
       </c>
@@ -4932,7 +5055,9 @@
       <c r="AB29" s="8">
         <v>13.446428571428571</v>
       </c>
-      <c r="AC29" s="8"/>
+      <c r="AC29" s="8">
+        <v>25.453498</v>
+      </c>
       <c r="AD29" s="8">
         <v>32.684443333333334</v>
       </c>
@@ -5057,7 +5182,9 @@
       <c r="AB30" s="8">
         <v>5.4855566666666666</v>
       </c>
-      <c r="AC30" s="8"/>
+      <c r="AC30" s="8">
+        <v>9.074999</v>
+      </c>
       <c r="AD30" s="8">
         <v>16.032776666666667</v>
       </c>
@@ -5188,7 +5315,9 @@
       <c r="AB31" s="8">
         <v>4.0554731343283583</v>
       </c>
-      <c r="AC31" s="8"/>
+      <c r="AC31" s="8">
+        <v>11.8818</v>
+      </c>
       <c r="AD31" s="8">
         <v>19.768382352941178</v>
       </c>
@@ -5317,7 +5446,9 @@
       <c r="AB32" s="8">
         <v>4.1774664000000001</v>
       </c>
-      <c r="AC32" s="8"/>
+      <c r="AC32" s="8">
+        <v>6.5927110000000004</v>
+      </c>
       <c r="AD32" s="8">
         <v>12.564533600000001</v>
       </c>
@@ -5444,7 +5575,9 @@
       <c r="AB33" s="8">
         <v>8.1626804347826081</v>
       </c>
-      <c r="AC33" s="8"/>
+      <c r="AC33" s="8">
+        <v>12.251688</v>
+      </c>
       <c r="AD33" s="8">
         <v>19.213406521739131</v>
       </c>
@@ -5644,10 +5777,10 @@
         <v>0.30769230769230771</v>
       </c>
       <c r="T35" s="6">
-        <v>0.19778235992010454</v>
+        <v>0.32508926667367505</v>
       </c>
       <c r="U35" s="6">
-        <v>-0.12698673915328818</v>
+        <v>0.0003201676002823374</v>
       </c>
       <c r="V35" s="6">
         <v>0.060255154910117591</v>
@@ -5670,7 +5803,9 @@
       <c r="AB35" s="8">
         <v>2.5570981481481483</v>
       </c>
-      <c r="AC35" s="8"/>
+      <c r="AC35" s="8">
+        <v>8.5780849999999997</v>
+      </c>
       <c r="AD35" s="8">
         <v>15.535185185185185</v>
       </c>
@@ -5896,7 +6031,9 @@
       <c r="AB37" s="8">
         <v>13.883153763440859</v>
       </c>
-      <c r="AC37" s="8"/>
+      <c r="AC37" s="8">
+        <v>29.511289999999999</v>
+      </c>
       <c r="AD37" s="8">
         <v>36.432437634408601</v>
       </c>
@@ -6025,7 +6162,9 @@
       <c r="AB38" s="8">
         <v>6.9483050847457628</v>
       </c>
-      <c r="AC38" s="8"/>
+      <c r="AC38" s="8">
+        <v>10.191046</v>
+      </c>
       <c r="AD38" s="8">
         <v>16.637903225806451</v>
       </c>
@@ -6076,7 +6215,7 @@
         <v>19565</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>44</v>
@@ -6112,25 +6251,61 @@
       <c t="s" r="N39" s="4">
         <v>52</v>
       </c>
-      <c r="O39" s="5"/>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="7"/>
-      <c r="S39" s="6"/>
-      <c r="T39" s="6"/>
-      <c r="U39" s="6"/>
-      <c r="V39" s="6"/>
-      <c r="W39" s="6"/>
-      <c r="X39" s="8"/>
-      <c r="Y39" s="6"/>
-      <c r="Z39" s="6"/>
-      <c r="AA39" s="8"/>
-      <c r="AB39" s="8"/>
-      <c r="AC39" s="8"/>
-      <c r="AD39" s="8"/>
-      <c r="AE39" s="6"/>
+      <c r="O39" s="5">
+        <v>10871.879999999999</v>
+      </c>
+      <c r="P39" s="5">
+        <v>10871.879999999999</v>
+      </c>
+      <c r="Q39" s="6">
+        <v>-0.27230011124453324</v>
+      </c>
+      <c r="R39" s="7">
+        <v>127</v>
+      </c>
+      <c r="S39" s="6">
+        <v>-0.28248587570621464</v>
+      </c>
+      <c r="T39" s="6">
+        <v>0.28185974274918413</v>
+      </c>
+      <c r="U39" s="6">
+        <v>-0.032635082432845103</v>
+      </c>
+      <c r="V39" s="6">
+        <v>0.074588157705934952</v>
+      </c>
+      <c r="W39" s="6">
+        <v>0.053485091814847119</v>
+      </c>
+      <c r="X39" s="8">
+        <v>26.846875000000001</v>
+      </c>
+      <c r="Y39" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z39" s="6">
+        <v>0.087499999999999994</v>
+      </c>
+      <c r="AA39" s="8">
+        <v>2.9110679687499998</v>
+      </c>
+      <c r="AB39" s="8">
+        <v>9.2858645569620251</v>
+      </c>
+      <c r="AC39" s="8">
+        <v>12.103559000000001</v>
+      </c>
+      <c r="AD39" s="8">
+        <v>19.81416625</v>
+      </c>
+      <c r="AE39" s="6">
+        <v>0.72499999999999998</v>
+      </c>
       <c r="AF39" s="9"/>
-      <c r="AG39" s="5"/>
+      <c r="AG39" s="5">
+        <v>0</v>
+      </c>
       <c r="AH39" s="10">
         <v>4</v>
       </c>
@@ -6249,7 +6424,9 @@
       <c r="AB40" s="8">
         <v>10.068009478672986</v>
       </c>
-      <c r="AC40" s="8"/>
+      <c r="AC40" s="8">
+        <v>17.018008999999999</v>
+      </c>
       <c r="AD40" s="8">
         <v>23.843946698113207</v>
       </c>
@@ -6378,7 +6555,9 @@
       <c r="AB41" s="8">
         <v>21.379118390804599</v>
       </c>
-      <c r="AC41" s="8"/>
+      <c r="AC41" s="8">
+        <v>24.990102</v>
+      </c>
       <c r="AD41" s="8">
         <v>30.581818181818178</v>
       </c>
@@ -6524,7 +6703,7 @@
         <v>19580</v>
       </c>
       <c r="B43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C43" s="4">
         <v>44</v>
@@ -6560,25 +6739,61 @@
       <c t="s" r="N43" s="4">
         <v>52</v>
       </c>
-      <c r="O43" s="5"/>
-      <c r="P43" s="5"/>
-      <c r="Q43" s="6"/>
-      <c r="R43" s="7"/>
-      <c r="S43" s="6"/>
-      <c r="T43" s="6"/>
-      <c r="U43" s="6"/>
-      <c r="V43" s="6"/>
-      <c r="W43" s="6"/>
-      <c r="X43" s="8"/>
-      <c r="Y43" s="6"/>
-      <c r="Z43" s="6"/>
-      <c r="AA43" s="8"/>
-      <c r="AB43" s="8"/>
-      <c r="AC43" s="8"/>
-      <c r="AD43" s="8"/>
-      <c r="AE43" s="6"/>
+      <c r="O43" s="5">
+        <v>9964.6800000000003</v>
+      </c>
+      <c r="P43" s="5">
+        <v>9964.6800000000003</v>
+      </c>
+      <c r="Q43" s="6">
+        <v>-0.045279081598923909</v>
+      </c>
+      <c r="R43" s="7">
+        <v>106</v>
+      </c>
+      <c r="S43" s="6">
+        <v>-0.094017094017094016</v>
+      </c>
+      <c r="T43" s="6">
+        <v>3.7974124608115865E-05</v>
+      </c>
+      <c r="U43" s="6">
+        <v>-0.32371050550544522</v>
+      </c>
+      <c r="V43" s="6">
+        <v>0.014844079288045377</v>
+      </c>
+      <c r="W43" s="6">
+        <v>-0.00010371632606365684</v>
+      </c>
+      <c r="X43" s="8">
+        <v>38.381818181818176</v>
+      </c>
+      <c r="Y43" s="6">
+        <v>0.39393939393939392</v>
+      </c>
+      <c r="Z43" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AA43" s="8">
+        <v>5.0436504761904759</v>
+      </c>
+      <c r="AB43" s="8">
+        <v>13.703846153846154</v>
+      </c>
+      <c r="AC43" s="8">
+        <v>19.440190000000001</v>
+      </c>
+      <c r="AD43" s="8">
+        <v>25.873989393939393</v>
+      </c>
+      <c r="AE43" s="6">
+        <v>0.090909090909090912</v>
+      </c>
       <c r="AF43" s="9"/>
-      <c r="AG43" s="5"/>
+      <c r="AG43" s="5">
+        <v>-105</v>
+      </c>
       <c r="AH43" s="10">
         <v>1</v>
       </c>
@@ -6697,7 +6912,9 @@
       <c r="AB44" s="8">
         <v>3.1805970149253731</v>
       </c>
-      <c r="AC44" s="8"/>
+      <c r="AC44" s="8">
+        <v>7.0924519999999998</v>
+      </c>
       <c r="AD44" s="8">
         <v>13.370486458333334</v>
       </c>
@@ -6826,7 +7043,9 @@
       <c r="AB45" s="8">
         <v>5.5622641509433963</v>
       </c>
-      <c r="AC45" s="8"/>
+      <c r="AC45" s="8">
+        <v>18.615742000000001</v>
+      </c>
       <c r="AD45" s="8">
         <v>24.855199082568806</v>
       </c>
@@ -6953,7 +7172,9 @@
       <c r="AB46" s="8">
         <v>6.4908490196078432</v>
       </c>
-      <c r="AC46" s="8"/>
+      <c r="AC46" s="8">
+        <v>8.8699329999999996</v>
+      </c>
       <c r="AD46" s="8">
         <v>15.819607843137254</v>
       </c>
@@ -7082,7 +7303,9 @@
       <c r="AB47" s="8">
         <v>11.756944444444445</v>
       </c>
-      <c r="AC47" s="8"/>
+      <c r="AC47" s="8">
+        <v>18.057410999999998</v>
+      </c>
       <c r="AD47" s="8">
         <v>24.952469444444446</v>
       </c>
@@ -7209,7 +7432,9 @@
       <c r="AB48" s="8">
         <v>8.2095824999999998</v>
       </c>
-      <c r="AC48" s="8"/>
+      <c r="AC48" s="8">
+        <v>28.763749000000001</v>
+      </c>
       <c r="AD48" s="8">
         <v>35.707917500000001</v>
       </c>
@@ -7260,7 +7485,7 @@
         <v>19600</v>
       </c>
       <c r="B49" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C49" s="4">
         <v>44</v>
@@ -7294,25 +7519,61 @@
       <c t="s" r="N49" s="4">
         <v>52</v>
       </c>
-      <c r="O49" s="5"/>
-      <c r="P49" s="5"/>
-      <c r="Q49" s="6"/>
-      <c r="R49" s="7"/>
-      <c r="S49" s="6"/>
-      <c r="T49" s="6"/>
-      <c r="U49" s="6"/>
-      <c r="V49" s="6"/>
-      <c r="W49" s="6"/>
-      <c r="X49" s="8"/>
-      <c r="Y49" s="6"/>
-      <c r="Z49" s="6"/>
-      <c r="AA49" s="8"/>
-      <c r="AB49" s="8"/>
-      <c r="AC49" s="8"/>
-      <c r="AD49" s="8"/>
-      <c r="AE49" s="6"/>
+      <c r="O49" s="5">
+        <v>8650.8299999999999</v>
+      </c>
+      <c r="P49" s="5">
+        <v>8650.8299999999999</v>
+      </c>
+      <c r="Q49" s="6">
+        <v>0.11534385394909874</v>
+      </c>
+      <c r="R49" s="7">
+        <v>98</v>
+      </c>
+      <c r="S49" s="6">
+        <v>-0.039215686274509776</v>
+      </c>
+      <c r="T49" s="6">
+        <v>0.0064097895808841471</v>
+      </c>
+      <c r="U49" s="6">
+        <v>-0.29675880811436589</v>
+      </c>
+      <c r="V49" s="6">
+        <v>0.028123081831454323</v>
+      </c>
+      <c r="W49" s="6">
+        <v>0.018851139139250222</v>
+      </c>
+      <c r="X49" s="8">
+        <v>25.897522972972972</v>
+      </c>
+      <c r="Y49" s="6">
+        <v>0.86486486486486491</v>
+      </c>
+      <c r="Z49" s="6">
+        <v>0.054054054054054057</v>
+      </c>
+      <c r="AA49" s="8">
+        <v>4.8166663157894734</v>
+      </c>
+      <c r="AB49" s="8">
+        <v>5.2378999999999998</v>
+      </c>
+      <c r="AC49" s="8">
+        <v>10.132268</v>
+      </c>
+      <c r="AD49" s="8">
+        <v>17.938063513513512</v>
+      </c>
+      <c r="AE49" s="6">
+        <v>0.77027027027027029</v>
+      </c>
       <c r="AF49" s="9"/>
-      <c r="AG49" s="5"/>
+      <c r="AG49" s="5">
+        <v>-3215.3000000000002</v>
+      </c>
       <c r="AH49" s="10">
         <v>3</v>
       </c>
@@ -7353,7 +7614,7 @@
         <v>19601</v>
       </c>
       <c r="B50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C50" s="4">
         <v>44</v>
@@ -7389,25 +7650,61 @@
       <c t="s" r="N50" s="4">
         <v>52</v>
       </c>
-      <c r="O50" s="5"/>
-      <c r="P50" s="5"/>
-      <c r="Q50" s="6"/>
-      <c r="R50" s="7"/>
-      <c r="S50" s="6"/>
-      <c r="T50" s="6"/>
-      <c r="U50" s="6"/>
-      <c r="V50" s="6"/>
-      <c r="W50" s="6"/>
-      <c r="X50" s="8"/>
-      <c r="Y50" s="6"/>
-      <c r="Z50" s="6"/>
-      <c r="AA50" s="8"/>
-      <c r="AB50" s="8"/>
-      <c r="AC50" s="8"/>
-      <c r="AD50" s="8"/>
-      <c r="AE50" s="6"/>
+      <c r="O50" s="5">
+        <v>9119.3299999999999</v>
+      </c>
+      <c r="P50" s="5">
+        <v>9119.3299999999999</v>
+      </c>
+      <c r="Q50" s="6">
+        <v>-0.32270249675252094</v>
+      </c>
+      <c r="R50" s="7">
+        <v>109</v>
+      </c>
+      <c r="S50" s="6">
+        <v>-0.29220779220779225</v>
+      </c>
+      <c r="T50" s="6">
+        <v>0.36102813474235496</v>
+      </c>
+      <c r="U50" s="6">
+        <v>0.071984970387078878</v>
+      </c>
+      <c r="V50" s="6">
+        <v>0.087317982790402371</v>
+      </c>
+      <c r="W50" s="6">
+        <v>0.059081259259178037</v>
+      </c>
+      <c r="X50" s="8">
+        <v>22.946504838709675</v>
+      </c>
+      <c r="Y50" s="6">
+        <v>0.967741935483871</v>
+      </c>
+      <c r="Z50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="8">
+        <v>2.9678690721649486</v>
+      </c>
+      <c r="AB50" s="8">
+        <v>4.5721311475409836</v>
+      </c>
+      <c r="AC50" s="8">
+        <v>7.6734530000000003</v>
+      </c>
+      <c r="AD50" s="8">
+        <v>15.471774193548388</v>
+      </c>
+      <c r="AE50" s="6">
+        <v>0.90322580645161288</v>
+      </c>
       <c r="AF50" s="9"/>
-      <c r="AG50" s="5"/>
+      <c r="AG50" s="5">
+        <v>0</v>
+      </c>
       <c r="AH50" s="10">
         <v>4</v>
       </c>
@@ -7621,7 +7918,9 @@
       <c r="AB52" s="8">
         <v>11.442791891891892</v>
       </c>
-      <c r="AC52" s="8"/>
+      <c r="AC52" s="8">
+        <v>21.350248000000001</v>
+      </c>
       <c r="AD52" s="8">
         <v>29.559910810810809</v>
       </c>
@@ -7672,7 +7971,7 @@
         <v>19607</v>
       </c>
       <c r="B53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C53" s="4">
         <v>44</v>
@@ -7706,25 +8005,61 @@
       <c t="s" r="N53" s="4">
         <v>52</v>
       </c>
-      <c r="O53" s="5"/>
-      <c r="P53" s="5"/>
-      <c r="Q53" s="6"/>
-      <c r="R53" s="7"/>
-      <c r="S53" s="6"/>
-      <c r="T53" s="6"/>
-      <c r="U53" s="6"/>
-      <c r="V53" s="6"/>
-      <c r="W53" s="6"/>
-      <c r="X53" s="8"/>
-      <c r="Y53" s="6"/>
-      <c r="Z53" s="6"/>
-      <c r="AA53" s="8"/>
-      <c r="AB53" s="8"/>
-      <c r="AC53" s="8"/>
-      <c r="AD53" s="8"/>
-      <c r="AE53" s="6"/>
+      <c r="O53" s="5">
+        <v>8913.6200000000008</v>
+      </c>
+      <c r="P53" s="5">
+        <v>8913.6200000000008</v>
+      </c>
+      <c r="Q53" s="6">
+        <v>0.22624614288288813</v>
+      </c>
+      <c r="R53" s="7">
+        <v>99</v>
+      </c>
+      <c r="S53" s="6">
+        <v>-0.010000000000000009</v>
+      </c>
+      <c r="T53" s="6">
+        <v>0.31860762518482943</v>
+      </c>
+      <c r="U53" s="6">
+        <v>-0.028562211536951314</v>
+      </c>
+      <c r="V53" s="6">
+        <v>0.03905276419681341</v>
+      </c>
+      <c r="W53" s="6">
+        <v>0.02008067429394567</v>
+      </c>
+      <c r="X53" s="8">
+        <v>25.13268039215686</v>
+      </c>
+      <c r="Y53" s="6">
+        <v>0.60784313725490191</v>
+      </c>
+      <c r="Z53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="8">
+        <v>3.7846797979797979</v>
+      </c>
+      <c r="AB53" s="8">
+        <v>2.8375823529411766</v>
+      </c>
+      <c r="AC53" s="8">
+        <v>6.5794110000000003</v>
+      </c>
+      <c r="AD53" s="8">
+        <v>13.507843137254902</v>
+      </c>
+      <c r="AE53" s="6">
+        <v>0.84313725490196079</v>
+      </c>
       <c r="AF53" s="9"/>
-      <c r="AG53" s="5"/>
+      <c r="AG53" s="5">
+        <v>0</v>
+      </c>
       <c r="AH53" s="10">
         <v>3</v>
       </c>
@@ -7843,7 +8178,9 @@
       <c r="AB54" s="8">
         <v>6.3145828125000003</v>
       </c>
-      <c r="AC54" s="8"/>
+      <c r="AC54" s="8">
+        <v>11.483487999999999</v>
+      </c>
       <c r="AD54" s="8">
         <v>18.341795384615384</v>
       </c>
@@ -7894,7 +8231,7 @@
         <v>19615</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>44</v>
@@ -7930,25 +8267,61 @@
       <c t="s" r="N55" s="4">
         <v>52</v>
       </c>
-      <c r="O55" s="5"/>
-      <c r="P55" s="5"/>
-      <c r="Q55" s="6"/>
-      <c r="R55" s="7"/>
-      <c r="S55" s="6"/>
-      <c r="T55" s="6"/>
-      <c r="U55" s="6"/>
-      <c r="V55" s="6"/>
-      <c r="W55" s="6"/>
-      <c r="X55" s="8"/>
-      <c r="Y55" s="6"/>
-      <c r="Z55" s="6"/>
-      <c r="AA55" s="8"/>
-      <c r="AB55" s="8"/>
-      <c r="AC55" s="8"/>
-      <c r="AD55" s="8"/>
-      <c r="AE55" s="6"/>
+      <c r="O55" s="5">
+        <v>9097.8299999999999</v>
+      </c>
+      <c r="P55" s="5">
+        <v>9097.8299999999999</v>
+      </c>
+      <c r="Q55" s="6">
+        <v>0.04489167286860174</v>
+      </c>
+      <c r="R55" s="7">
+        <v>106</v>
+      </c>
+      <c r="S55" s="6">
+        <v>0.070707070707070718</v>
+      </c>
+      <c r="T55" s="6">
+        <v>9.5627199013391105E-05</v>
+      </c>
+      <c r="U55" s="6">
+        <v>-0.32648884404303008</v>
+      </c>
+      <c r="V55" s="6">
+        <v>0.078456785848933216</v>
+      </c>
+      <c r="W55" s="6">
+        <v>0.043910086251336855</v>
+      </c>
+      <c r="X55" s="8">
+        <v>58.656043956043952</v>
+      </c>
+      <c r="Y55" s="6">
+        <v>0.01098901098901099</v>
+      </c>
+      <c r="Z55" s="6">
+        <v>0.76923076923076927</v>
+      </c>
+      <c r="AA55" s="8">
+        <v>2.5130955357142857</v>
+      </c>
+      <c r="AB55" s="8">
+        <v>35.17912087912088</v>
+      </c>
+      <c r="AC55" s="8">
+        <v>37.608829999999998</v>
+      </c>
+      <c r="AD55" s="8">
+        <v>41.394569662921349</v>
+      </c>
+      <c r="AE55" s="6">
+        <v>0.043956043956043959</v>
+      </c>
       <c r="AF55" s="9"/>
-      <c r="AG55" s="5"/>
+      <c r="AG55" s="5">
+        <v>0</v>
+      </c>
       <c r="AH55" s="10">
         <v>2</v>
       </c>
@@ -8065,7 +8438,9 @@
       <c r="AB56" s="8">
         <v>6.7889320312499999</v>
       </c>
-      <c r="AC56" s="8"/>
+      <c r="AC56" s="8">
+        <v>12.039054</v>
+      </c>
       <c r="AD56" s="8">
         <v>19.98604962962963</v>
       </c>
@@ -8194,7 +8569,9 @@
       <c r="AB57" s="8">
         <v>6.6396299999999995</v>
       </c>
-      <c r="AC57" s="8"/>
+      <c r="AC57" s="8">
+        <v>19.868016999999998</v>
+      </c>
       <c r="AD57" s="8">
         <v>26.903518888888886</v>
       </c>
@@ -8418,7 +8795,9 @@
       <c r="AB59" s="8">
         <v>8.4075471698113216</v>
       </c>
-      <c r="AC59" s="8"/>
+      <c r="AC59" s="8">
+        <v>12.410273999999999</v>
+      </c>
       <c r="AD59" s="8">
         <v>18.951212727272729</v>
       </c>
@@ -8469,7 +8848,7 @@
         <v>19623</v>
       </c>
       <c r="B60" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C60" s="4">
         <v>44</v>
@@ -8505,25 +8884,61 @@
       <c t="s" r="N60" s="4">
         <v>52</v>
       </c>
-      <c r="O60" s="5"/>
-      <c r="P60" s="5"/>
-      <c r="Q60" s="6"/>
-      <c r="R60" s="7"/>
-      <c r="S60" s="6"/>
-      <c r="T60" s="6"/>
-      <c r="U60" s="6"/>
-      <c r="V60" s="6"/>
-      <c r="W60" s="6"/>
-      <c r="X60" s="8"/>
-      <c r="Y60" s="6"/>
-      <c r="Z60" s="6"/>
-      <c r="AA60" s="8"/>
-      <c r="AB60" s="8"/>
-      <c r="AC60" s="8"/>
-      <c r="AD60" s="8"/>
-      <c r="AE60" s="6"/>
+      <c r="O60" s="5">
+        <v>7484.6400000000003</v>
+      </c>
+      <c r="P60" s="5">
+        <v>7484.6400000000003</v>
+      </c>
+      <c r="Q60" s="6">
+        <v>-0.12124883766800987</v>
+      </c>
+      <c r="R60" s="7">
+        <v>84</v>
+      </c>
+      <c r="S60" s="6">
+        <v>-0.16000000000000003</v>
+      </c>
+      <c r="T60" s="6">
+        <v>0.29734134173453902</v>
+      </c>
+      <c r="U60" s="6">
+        <v>-0.011028867119861476</v>
+      </c>
+      <c r="V60" s="6">
+        <v>0.023297713717693836</v>
+      </c>
+      <c r="W60" s="6">
+        <v>0.0055947914662562255</v>
+      </c>
+      <c r="X60" s="8">
+        <v>24.627478378378377</v>
+      </c>
+      <c r="Y60" s="6">
+        <v>0.94594594594594594</v>
+      </c>
+      <c r="Z60" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="8">
+        <v>2.9127087499999997</v>
+      </c>
+      <c r="AB60" s="8">
+        <v>4.0171162162162162</v>
+      </c>
+      <c r="AC60" s="8">
+        <v>6.913062</v>
+      </c>
+      <c r="AD60" s="8">
+        <v>14.878829729729731</v>
+      </c>
+      <c r="AE60" s="6">
+        <v>0.7567567567567568</v>
+      </c>
       <c r="AF60" s="9"/>
-      <c r="AG60" s="5"/>
+      <c r="AG60" s="5">
+        <v>-104.7</v>
+      </c>
       <c r="AH60" s="10">
         <v>4</v>
       </c>
@@ -8640,7 +9055,9 @@
       <c r="AB61" s="8">
         <v>5.6284090909090914</v>
       </c>
-      <c r="AC61" s="8"/>
+      <c r="AC61" s="8">
+        <v>7.9092060000000002</v>
+      </c>
       <c r="AD61" s="8">
         <v>14.357245652173914</v>
       </c>
@@ -8689,7 +9106,7 @@
         <v>19625</v>
       </c>
       <c r="B62" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C62" s="4">
         <v>44</v>
@@ -8725,25 +9142,61 @@
       <c t="s" r="N62" s="4">
         <v>52</v>
       </c>
-      <c r="O62" s="5"/>
-      <c r="P62" s="5"/>
-      <c r="Q62" s="6"/>
-      <c r="R62" s="7"/>
-      <c r="S62" s="6"/>
-      <c r="T62" s="6"/>
-      <c r="U62" s="6"/>
-      <c r="V62" s="6"/>
-      <c r="W62" s="6"/>
-      <c r="X62" s="8"/>
-      <c r="Y62" s="6"/>
-      <c r="Z62" s="6"/>
-      <c r="AA62" s="8"/>
-      <c r="AB62" s="8"/>
-      <c r="AC62" s="8"/>
-      <c r="AD62" s="8"/>
-      <c r="AE62" s="6"/>
+      <c r="O62" s="5">
+        <v>13649.139999999999</v>
+      </c>
+      <c r="P62" s="5">
+        <v>13649.139999999999</v>
+      </c>
+      <c r="Q62" s="6">
+        <v>-0.14338450338274611</v>
+      </c>
+      <c r="R62" s="7">
+        <v>124</v>
+      </c>
+      <c r="S62" s="6">
+        <v>-0.27906976744186052</v>
+      </c>
+      <c r="T62" s="6">
+        <v>-1.8059745888751965E-05</v>
+      </c>
+      <c r="U62" s="6">
+        <v>-0.30044284841389279</v>
+      </c>
+      <c r="V62" s="6">
+        <v>0.029480868391708197</v>
+      </c>
+      <c r="W62" s="6">
+        <v>0.019856086170996858</v>
+      </c>
+      <c r="X62" s="8">
+        <v>29.372950819672131</v>
+      </c>
+      <c r="Y62" s="6">
+        <v>0.50819672131147542</v>
+      </c>
+      <c r="Z62" s="6">
+        <v>0.13114754098360656</v>
+      </c>
+      <c r="AA62" s="8">
+        <v>6.0167999999999999</v>
+      </c>
+      <c r="AB62" s="8">
+        <v>7.6571032786885249</v>
+      </c>
+      <c r="AC62" s="8">
+        <v>14.041759000000001</v>
+      </c>
+      <c r="AD62" s="8">
+        <v>20.822131147540986</v>
+      </c>
+      <c r="AE62" s="6">
+        <v>0.55737704918032782</v>
+      </c>
       <c r="AF62" s="9"/>
-      <c r="AG62" s="5"/>
+      <c r="AG62" s="5">
+        <v>0</v>
+      </c>
       <c r="AH62" s="10">
         <v>4</v>
       </c>
@@ -8862,7 +9315,9 @@
       <c r="AB63" s="8">
         <v>9.423246052631578</v>
       </c>
-      <c r="AC63" s="8"/>
+      <c r="AC63" s="8">
+        <v>13.018483</v>
+      </c>
       <c r="AD63" s="8">
         <v>18.772727272727273</v>
       </c>
@@ -8989,7 +9444,9 @@
       <c r="AB64" s="8">
         <v>8.1085594594594603</v>
       </c>
-      <c r="AC64" s="8"/>
+      <c r="AC64" s="8">
+        <v>11.990136</v>
+      </c>
       <c r="AD64" s="8">
         <v>18.58421052631579</v>
       </c>
@@ -9211,7 +9668,9 @@
       <c r="AB66" s="8">
         <v>4.7146265306122448</v>
       </c>
-      <c r="AC66" s="8"/>
+      <c r="AC66" s="8">
+        <v>8.8360529999999997</v>
+      </c>
       <c r="AD66" s="8">
         <v>15.775851020408163</v>
       </c>
@@ -9338,7 +9797,9 @@
       <c r="AB67" s="8">
         <v>11.539352777777777</v>
       </c>
-      <c r="AC67" s="8"/>
+      <c r="AC67" s="8">
+        <v>15.523999999999999</v>
+      </c>
       <c r="AD67" s="8">
         <v>21.659210526315789</v>
       </c>
@@ -9467,7 +9928,9 @@
       <c r="AB68" s="8">
         <v>7.6833333333333327</v>
       </c>
-      <c r="AC68" s="8"/>
+      <c r="AC68" s="8">
+        <v>23.008928000000001</v>
+      </c>
       <c r="AD68" s="8">
         <v>29.864545454545453</v>
       </c>
@@ -9590,7 +10053,9 @@
       <c r="AB69" s="8">
         <v>6.3869053571428571</v>
       </c>
-      <c r="AC69" s="8"/>
+      <c r="AC69" s="8">
+        <v>12.802158</v>
+      </c>
       <c r="AD69" s="8">
         <v>20.483046551724136</v>
       </c>
@@ -9719,7 +10184,9 @@
       <c r="AB70" s="8">
         <v>9.4423076923076916</v>
       </c>
-      <c r="AC70" s="8"/>
+      <c r="AC70" s="8">
+        <v>16.818449999999999</v>
+      </c>
       <c r="AD70" s="8">
         <v>23.624359615384613</v>
       </c>
@@ -9770,7 +10237,7 @@
         <v>19649</v>
       </c>
       <c r="B71" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C71" s="4">
         <v>44</v>
@@ -9804,25 +10271,61 @@
       <c t="s" r="N71" s="4">
         <v>52</v>
       </c>
-      <c r="O71" s="5"/>
-      <c r="P71" s="5"/>
-      <c r="Q71" s="6"/>
-      <c r="R71" s="7"/>
-      <c r="S71" s="6"/>
-      <c r="T71" s="6"/>
-      <c r="U71" s="6"/>
-      <c r="V71" s="6"/>
-      <c r="W71" s="6"/>
-      <c r="X71" s="8"/>
-      <c r="Y71" s="6"/>
-      <c r="Z71" s="6"/>
-      <c r="AA71" s="8"/>
-      <c r="AB71" s="8"/>
-      <c r="AC71" s="8"/>
-      <c r="AD71" s="8"/>
-      <c r="AE71" s="6"/>
+      <c r="O71" s="5">
+        <v>12009.25</v>
+      </c>
+      <c r="P71" s="5">
+        <v>12009.25</v>
+      </c>
+      <c r="Q71" s="6">
+        <v>-0.24063555375415668</v>
+      </c>
+      <c r="R71" s="7">
+        <v>143</v>
+      </c>
+      <c r="S71" s="6">
+        <v>-0.24338624338624337</v>
+      </c>
+      <c r="T71" s="6">
+        <v>0.25931894997606009</v>
+      </c>
+      <c r="U71" s="6">
+        <v>-0.050869446468347318</v>
+      </c>
+      <c r="V71" s="6">
+        <v>0.044058829652143146</v>
+      </c>
+      <c r="W71" s="6">
+        <v>0.018870745467035828</v>
+      </c>
+      <c r="X71" s="8">
+        <v>19.920369841269842</v>
+      </c>
+      <c r="Y71" s="6">
+        <v>0.84126984126984128</v>
+      </c>
+      <c r="Z71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="8">
+        <v>2.7503649635036496</v>
+      </c>
+      <c r="AB71" s="8">
+        <v>1.9073105263157895</v>
+      </c>
+      <c r="AC71" s="8">
+        <v>4.7319940000000003</v>
+      </c>
+      <c r="AD71" s="8">
+        <v>12.167195238095239</v>
+      </c>
+      <c r="AE71" s="6">
+        <v>0.95238095238095233</v>
+      </c>
       <c r="AF71" s="9"/>
-      <c r="AG71" s="5"/>
+      <c r="AG71" s="5">
+        <v>-154.69999999999999</v>
+      </c>
       <c r="AH71" s="10">
         <v>4</v>
       </c>
@@ -9939,7 +10442,9 @@
       <c r="AB72" s="8">
         <v>5.712065644171779</v>
       </c>
-      <c r="AC72" s="8"/>
+      <c r="AC72" s="8">
+        <v>16.260245999999999</v>
+      </c>
       <c r="AD72" s="8">
         <v>23.143190853658535</v>
       </c>
@@ -10066,7 +10571,9 @@
       <c r="AB73" s="8">
         <v>6.3120370370370376</v>
       </c>
-      <c r="AC73" s="8"/>
+      <c r="AC73" s="8">
+        <v>9.017989</v>
+      </c>
       <c r="AD73" s="8">
         <v>16.695237500000001</v>
       </c>
@@ -10208,7 +10715,7 @@
         <v>19657</v>
       </c>
       <c r="B75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C75" s="4">
         <v>44</v>
@@ -10244,25 +10751,61 @@
       <c t="s" r="N75" s="4">
         <v>52</v>
       </c>
-      <c r="O75" s="5"/>
-      <c r="P75" s="5"/>
-      <c r="Q75" s="6"/>
-      <c r="R75" s="7"/>
-      <c r="S75" s="6"/>
-      <c r="T75" s="6"/>
-      <c r="U75" s="6"/>
-      <c r="V75" s="6"/>
-      <c r="W75" s="6"/>
-      <c r="X75" s="8"/>
-      <c r="Y75" s="6"/>
-      <c r="Z75" s="6"/>
-      <c r="AA75" s="8"/>
-      <c r="AB75" s="8"/>
-      <c r="AC75" s="8"/>
-      <c r="AD75" s="8"/>
-      <c r="AE75" s="6"/>
+      <c r="O75" s="5">
+        <v>8006.3400000000001</v>
+      </c>
+      <c r="P75" s="5">
+        <v>8006.3400000000001</v>
+      </c>
+      <c r="Q75" s="6">
+        <v>0.26237567562453878</v>
+      </c>
+      <c r="R75" s="7">
+        <v>87</v>
+      </c>
+      <c r="S75" s="6">
+        <v>0.11538461538461542</v>
+      </c>
+      <c r="T75" s="6">
+        <v>0</v>
+      </c>
+      <c r="U75" s="6">
+        <v>-0.32346490406352962</v>
+      </c>
+      <c r="V75" s="6">
+        <v>0.050580977075667534</v>
+      </c>
+      <c r="W75" s="6">
+        <v>0.035845155214492511</v>
+      </c>
+      <c r="X75" s="8">
+        <v>27.114913157894737</v>
+      </c>
+      <c r="Y75" s="6">
+        <v>0.84210526315789469</v>
+      </c>
+      <c r="Z75" s="6">
+        <v>0.078947368421052627</v>
+      </c>
+      <c r="AA75" s="8">
+        <v>7.1345094117647063</v>
+      </c>
+      <c r="AB75" s="8">
+        <v>7.3031540540540538</v>
+      </c>
+      <c r="AC75" s="8">
+        <v>14.32596</v>
+      </c>
+      <c r="AD75" s="8">
+        <v>20.887718421052632</v>
+      </c>
+      <c r="AE75" s="6">
+        <v>0.65789473684210531</v>
+      </c>
       <c r="AF75" s="9"/>
-      <c r="AG75" s="5"/>
+      <c r="AG75" s="5">
+        <v>-541.79999999999995</v>
+      </c>
       <c r="AH75" s="10">
         <v>3</v>
       </c>
@@ -10474,7 +11017,9 @@
       <c r="AB77" s="8">
         <v>2.5296963636363636</v>
       </c>
-      <c r="AC77" s="8"/>
+      <c r="AC77" s="8">
+        <v>9.1718170000000008</v>
+      </c>
       <c r="AD77" s="8">
         <v>16.112423636363637</v>
       </c>
@@ -10523,7 +11068,7 @@
         <v>19666</v>
       </c>
       <c r="B78" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C78" s="4">
         <v>44</v>
@@ -10557,25 +11102,61 @@
       <c t="s" r="N78" s="4">
         <v>52</v>
       </c>
-      <c r="O78" s="5"/>
-      <c r="P78" s="5"/>
-      <c r="Q78" s="6"/>
-      <c r="R78" s="7"/>
-      <c r="S78" s="6"/>
-      <c r="T78" s="6"/>
-      <c r="U78" s="6"/>
-      <c r="V78" s="6"/>
-      <c r="W78" s="6"/>
-      <c r="X78" s="8"/>
-      <c r="Y78" s="6"/>
-      <c r="Z78" s="6"/>
-      <c r="AA78" s="8"/>
-      <c r="AB78" s="8"/>
-      <c r="AC78" s="8"/>
-      <c r="AD78" s="8"/>
-      <c r="AE78" s="6"/>
+      <c r="O78" s="5">
+        <v>13753.17</v>
+      </c>
+      <c r="P78" s="5">
+        <v>13753.17</v>
+      </c>
+      <c r="Q78" s="6">
+        <v>0.034225344486856546</v>
+      </c>
+      <c r="R78" s="7">
+        <v>135</v>
+      </c>
+      <c r="S78" s="6">
+        <v>0</v>
+      </c>
+      <c r="T78" s="6">
+        <v>1.0695700191301352</v>
+      </c>
+      <c r="U78" s="6">
+        <v>0.75651128430754511</v>
+      </c>
+      <c r="V78" s="6">
+        <v>0.015390488156548636</v>
+      </c>
+      <c r="W78" s="6">
+        <v>0.0032914593508260276</v>
+      </c>
+      <c r="X78" s="8">
+        <v>20.94663085106383</v>
+      </c>
+      <c r="Y78" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z78" s="6">
+        <v>0.010638297872340425</v>
+      </c>
+      <c r="AA78" s="8">
+        <v>2.3910536764705879</v>
+      </c>
+      <c r="AB78" s="8">
+        <v>4.1068096774193545</v>
+      </c>
+      <c r="AC78" s="8">
+        <v>6.4906689999999996</v>
+      </c>
+      <c r="AD78" s="8">
+        <v>14.396630851063831</v>
+      </c>
+      <c r="AE78" s="6">
+        <v>0.96808510638297873</v>
+      </c>
       <c r="AF78" s="9"/>
-      <c r="AG78" s="5"/>
+      <c r="AG78" s="5">
+        <v>-80.799999999999997</v>
+      </c>
       <c r="AH78" s="10">
         <v>5</v>
       </c>
@@ -10694,7 +11275,9 @@
       <c r="AB79" s="8">
         <v>13.49423076923077</v>
       </c>
-      <c r="AC79" s="8"/>
+      <c r="AC79" s="8">
+        <v>20.769072000000001</v>
+      </c>
       <c r="AD79" s="8">
         <v>27.422956603773585</v>
       </c>
@@ -10821,7 +11404,9 @@
       <c r="AB80" s="8">
         <v>7.2035211267605632</v>
       </c>
-      <c r="AC80" s="8"/>
+      <c r="AC80" s="8">
+        <v>13.312179</v>
+      </c>
       <c r="AD80" s="8">
         <v>22.458658441558441</v>
       </c>
@@ -10948,7 +11533,9 @@
       <c r="AB81" s="8">
         <v>1.2745631578947367</v>
       </c>
-      <c r="AC81" s="8"/>
+      <c r="AC81" s="8">
+        <v>3.408687</v>
+      </c>
       <c r="AD81" s="8">
         <v>9.7928571428571427</v>
       </c>
@@ -11077,7 +11664,9 @@
       <c r="AB82" s="8">
         <v>6.3875000000000002</v>
       </c>
-      <c r="AC82" s="8"/>
+      <c r="AC82" s="8">
+        <v>14.029947</v>
+      </c>
       <c r="AD82" s="8">
         <v>20.948176562499999</v>
       </c>
@@ -11299,7 +11888,9 @@
       <c r="AB84" s="8">
         <v>9.0829268292682919</v>
       </c>
-      <c r="AC84" s="8"/>
+      <c r="AC84" s="8">
+        <v>15.50737</v>
+      </c>
       <c r="AD84" s="8">
         <v>21.393333333333334</v>
       </c>
@@ -11426,7 +12017,9 @@
       <c r="AB85" s="8">
         <v>39.281477777777781</v>
       </c>
-      <c r="AC85" s="8"/>
+      <c r="AC85" s="8">
+        <v>47.625419999999998</v>
+      </c>
       <c r="AD85" s="8">
         <v>54.070366666666672</v>
       </c>
@@ -11555,7 +12148,9 @@
       <c r="AB86" s="8">
         <v>5.9706054545454545</v>
       </c>
-      <c r="AC86" s="8"/>
+      <c r="AC86" s="8">
+        <v>12.943636</v>
+      </c>
       <c r="AD86" s="8">
         <v>21.387272727272727</v>
       </c>
@@ -11684,7 +12279,9 @@
       <c r="AB87" s="8">
         <v>1.9722238095238094</v>
       </c>
-      <c r="AC87" s="8"/>
+      <c r="AC87" s="8">
+        <v>4.3722219999999998</v>
+      </c>
       <c r="AD87" s="8">
         <v>7.4613207547169811</v>
       </c>
@@ -11811,7 +12408,9 @@
       <c r="AB88" s="8">
         <v>4.9570175438596493</v>
       </c>
-      <c r="AC88" s="8"/>
+      <c r="AC88" s="8">
+        <v>7.738626</v>
+      </c>
       <c r="AD88" s="8">
         <v>13.885918965517241</v>
       </c>
@@ -12033,7 +12632,9 @@
       <c r="AB90" s="8">
         <v>13.173189130434782</v>
       </c>
-      <c r="AC90" s="8"/>
+      <c r="AC90" s="8">
+        <v>17.611955999999999</v>
+      </c>
       <c r="AD90" s="8">
         <v>24.516304347826086</v>
       </c>
@@ -12162,7 +12763,9 @@
       <c r="AB91" s="8">
         <v>9.4022442307692309</v>
       </c>
-      <c r="AC91" s="8"/>
+      <c r="AC91" s="8">
+        <v>14.911047999999999</v>
+      </c>
       <c r="AD91" s="8">
         <v>21.612579245283019</v>
       </c>
@@ -12291,7 +12894,9 @@
       <c r="AB92" s="8">
         <v>8.1640159090909084</v>
       </c>
-      <c r="AC92" s="8"/>
+      <c r="AC92" s="8">
+        <v>15.135605</v>
+      </c>
       <c r="AD92" s="8">
         <v>23.046211363636363</v>
       </c>
@@ -12418,7 +13023,9 @@
       <c r="AB93" s="8">
         <v>2.6554389473684208</v>
       </c>
-      <c r="AC93" s="8"/>
+      <c r="AC93" s="8">
+        <v>5.0710730000000002</v>
+      </c>
       <c r="AD93" s="8">
         <v>11.893642268041237</v>
       </c>
@@ -12545,7 +13152,9 @@
       <c r="AB94" s="8">
         <v>4.1791084507042253</v>
       </c>
-      <c r="AC94" s="8"/>
+      <c r="AC94" s="8">
+        <v>8.3417189999999994</v>
+      </c>
       <c r="AD94" s="8">
         <v>15.902702702702703</v>
       </c>
@@ -12767,7 +13376,9 @@
       <c r="AB96" s="8">
         <v>8.2950392857142869</v>
       </c>
-      <c r="AC96" s="8"/>
+      <c r="AC96" s="8">
+        <v>14.607391</v>
+      </c>
       <c r="AD96" s="8">
         <v>21.550991666666668</v>
       </c>
@@ -12896,7 +13507,9 @@
       <c r="AB97" s="8">
         <v>4.2580448275862066</v>
       </c>
-      <c r="AC97" s="8"/>
+      <c r="AC97" s="8">
+        <v>7.6791559999999999</v>
+      </c>
       <c r="AD97" s="8">
         <v>13.42389</v>
       </c>
@@ -13025,7 +13638,9 @@
       <c r="AB98" s="8">
         <v>10.607264102564102</v>
       </c>
-      <c r="AC98" s="8"/>
+      <c r="AC98" s="8">
+        <v>18.505279000000002</v>
+      </c>
       <c r="AD98" s="8">
         <v>24.490476190476187</v>
       </c>
@@ -13154,7 +13769,9 @@
       <c r="AB99" s="8">
         <v>3.7882109756097564</v>
       </c>
-      <c r="AC99" s="8"/>
+      <c r="AC99" s="8">
+        <v>7.8247960000000001</v>
+      </c>
       <c r="AD99" s="8">
         <v>14.770121951219513</v>
       </c>
@@ -13205,7 +13822,7 @@
         <v>19715</v>
       </c>
       <c r="B100" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C100" s="4">
         <v>44</v>
@@ -13241,25 +13858,61 @@
       <c t="s" r="N100" s="4">
         <v>52</v>
       </c>
-      <c r="O100" s="5"/>
-      <c r="P100" s="5"/>
-      <c r="Q100" s="6"/>
-      <c r="R100" s="7"/>
-      <c r="S100" s="6"/>
-      <c r="T100" s="6"/>
-      <c r="U100" s="6"/>
-      <c r="V100" s="6"/>
-      <c r="W100" s="6"/>
-      <c r="X100" s="8"/>
-      <c r="Y100" s="6"/>
-      <c r="Z100" s="6"/>
-      <c r="AA100" s="8"/>
-      <c r="AB100" s="8"/>
-      <c r="AC100" s="8"/>
-      <c r="AD100" s="8"/>
-      <c r="AE100" s="6"/>
+      <c r="O100" s="5">
+        <v>11346.799999999999</v>
+      </c>
+      <c r="P100" s="5">
+        <v>11346.799999999999</v>
+      </c>
+      <c r="Q100" s="6">
+        <v>1.0364912935635906</v>
+      </c>
+      <c r="R100" s="7">
+        <v>113</v>
+      </c>
+      <c r="S100" s="6">
+        <v>0.68656716417910446</v>
+      </c>
+      <c r="T100" s="6">
+        <v>0</v>
+      </c>
+      <c r="U100" s="6">
+        <v>-0.38832974935664683</v>
+      </c>
+      <c r="V100" s="6">
+        <v>0.060576638347375478</v>
+      </c>
+      <c r="W100" s="6">
+        <v>0.043103870694821453</v>
+      </c>
+      <c r="X100" s="8">
+        <v>47.59890394736842</v>
+      </c>
+      <c r="Y100" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z100" s="6">
+        <v>0.64473684210526316</v>
+      </c>
+      <c r="AA100" s="8">
+        <v>14.047492920353983</v>
+      </c>
+      <c r="AB100" s="8">
+        <v>18.489911842105265</v>
+      </c>
+      <c r="AC100" s="8">
+        <v>34.250875999999998</v>
+      </c>
+      <c r="AD100" s="8">
+        <v>43.209648684210528</v>
+      </c>
+      <c r="AE100" s="6">
+        <v>0.17105263157894737</v>
+      </c>
       <c r="AF100" s="9"/>
-      <c r="AG100" s="5"/>
+      <c r="AG100" s="5">
+        <v>-140.59999999999999</v>
+      </c>
       <c r="AH100" s="10">
         <v>3</v>
       </c>
@@ -13376,7 +14029,9 @@
       <c r="AB101" s="8">
         <v>24.634333999999999</v>
       </c>
-      <c r="AC101" s="8"/>
+      <c r="AC101" s="8">
+        <v>26.446332999999999</v>
+      </c>
       <c r="AD101" s="8">
         <v>33.326999999999998</v>
       </c>
@@ -13427,7 +14082,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>44</v>
@@ -13463,25 +14118,61 @@
       <c t="s" r="N102" s="4">
         <v>52</v>
       </c>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="8"/>
-      <c r="AB102" s="8"/>
-      <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="6"/>
+      <c r="O102" s="5">
+        <v>7369.04</v>
+      </c>
+      <c r="P102" s="5">
+        <v>7369.04</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>-0.25710604604929554</v>
+      </c>
+      <c r="R102" s="7">
+        <v>73</v>
+      </c>
+      <c r="S102" s="6">
+        <v>-0.33027522935779818</v>
+      </c>
+      <c r="T102" s="6">
+        <v>0.0001540770575271677</v>
+      </c>
+      <c r="U102" s="6">
+        <v>-0.33323534680229722</v>
+      </c>
+      <c r="V102" s="6">
+        <v>0.01388240530652568</v>
+      </c>
+      <c r="W102" s="6">
+        <v>0.00061744813435671406</v>
+      </c>
+      <c r="X102" s="8">
+        <v>48.501361224489791</v>
+      </c>
+      <c r="Y102" s="6">
+        <v>0.081632653061224483</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>0.59183673469387754</v>
+      </c>
+      <c r="AA102" s="8">
+        <v>11.819406849315069</v>
+      </c>
+      <c r="AB102" s="8">
+        <v>14.854255319148935</v>
+      </c>
+      <c r="AC102" s="8">
+        <v>27.302893999999998</v>
+      </c>
+      <c r="AD102" s="8">
+        <v>33.259183673469387</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0.10204081632653061</v>
+      </c>
       <c r="AF102" s="9"/>
-      <c r="AG102" s="5"/>
+      <c r="AG102" s="5">
+        <v>-130.69999999999999</v>
+      </c>
       <c r="AH102" s="10">
         <v>2</v>
       </c>
@@ -13600,7 +14291,9 @@
       <c r="AB103" s="8">
         <v>3.9640733333333333</v>
       </c>
-      <c r="AC103" s="8"/>
+      <c r="AC103" s="8">
+        <v>13.360332</v>
+      </c>
       <c r="AD103" s="8">
         <v>19.270921276595743</v>
       </c>
@@ -13729,7 +14422,9 @@
       <c r="AB104" s="8">
         <v>1.7423604166666669</v>
       </c>
-      <c r="AC104" s="8"/>
+      <c r="AC104" s="8">
+        <v>6.5080270000000002</v>
+      </c>
       <c r="AD104" s="8">
         <v>14.831666</v>
       </c>
@@ -13856,7 +14551,9 @@
       <c r="AB105" s="8">
         <v>8.862255882352942</v>
       </c>
-      <c r="AC105" s="8"/>
+      <c r="AC105" s="8">
+        <v>12.602166</v>
+      </c>
       <c r="AD105" s="8">
         <v>17.848197297297297</v>
       </c>
@@ -13985,7 +14682,9 @@
       <c r="AB106" s="8">
         <v>1.413674358974359</v>
       </c>
-      <c r="AC106" s="8"/>
+      <c r="AC106" s="8">
+        <v>10.594682000000001</v>
+      </c>
       <c r="AD106" s="8">
         <v>17.752917500000002</v>
       </c>
@@ -14036,7 +14735,7 @@
         <v>19727</v>
       </c>
       <c r="B107" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C107" s="4">
         <v>44</v>
@@ -14072,25 +14771,61 @@
       <c t="s" r="N107" s="4">
         <v>52</v>
       </c>
-      <c r="O107" s="5"/>
-      <c r="P107" s="5"/>
-      <c r="Q107" s="6"/>
-      <c r="R107" s="7"/>
-      <c r="S107" s="6"/>
-      <c r="T107" s="6"/>
-      <c r="U107" s="6"/>
-      <c r="V107" s="6"/>
-      <c r="W107" s="6"/>
-      <c r="X107" s="8"/>
-      <c r="Y107" s="6"/>
-      <c r="Z107" s="6"/>
-      <c r="AA107" s="8"/>
-      <c r="AB107" s="8"/>
-      <c r="AC107" s="8"/>
-      <c r="AD107" s="8"/>
-      <c r="AE107" s="6"/>
+      <c r="O107" s="5">
+        <v>6452.0500000000002</v>
+      </c>
+      <c r="P107" s="5">
+        <v>6452.0500000000002</v>
+      </c>
+      <c r="Q107" s="6">
+        <v>-0.078431288529329346</v>
+      </c>
+      <c r="R107" s="7">
+        <v>83</v>
+      </c>
+      <c r="S107" s="6">
+        <v>-0.087912087912087933</v>
+      </c>
+      <c r="T107" s="6">
+        <v>0.21663883571888004</v>
+      </c>
+      <c r="U107" s="6">
+        <v>-0.12411332832200618</v>
+      </c>
+      <c r="V107" s="6">
+        <v>0.017498624468192281</v>
+      </c>
+      <c r="W107" s="6">
+        <v>-0.0051670399330445366</v>
+      </c>
+      <c r="X107" s="8">
+        <v>24.755150909090911</v>
+      </c>
+      <c r="Y107" s="6">
+        <v>0.78181818181818186</v>
+      </c>
+      <c r="Z107" s="6">
+        <v>0.018181818181818181</v>
+      </c>
+      <c r="AA107" s="8">
+        <v>4.6012048192771084</v>
+      </c>
+      <c r="AB107" s="8">
+        <v>5.4003274509803916</v>
+      </c>
+      <c r="AC107" s="8">
+        <v>10.24854</v>
+      </c>
+      <c r="AD107" s="8">
+        <v>16.579090909090908</v>
+      </c>
+      <c r="AE107" s="6">
+        <v>0.78181818181818186</v>
+      </c>
       <c r="AF107" s="9"/>
-      <c r="AG107" s="5"/>
+      <c r="AG107" s="5">
+        <v>-103.8</v>
+      </c>
       <c r="AH107" s="10">
         <v>2</v>
       </c>
@@ -14224,7 +14959,7 @@
         <v>19730</v>
       </c>
       <c r="B109" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C109" s="4">
         <v>44</v>
@@ -14258,25 +14993,61 @@
       <c t="s" r="N109" s="4">
         <v>52</v>
       </c>
-      <c r="O109" s="5"/>
-      <c r="P109" s="5"/>
-      <c r="Q109" s="6"/>
-      <c r="R109" s="7"/>
-      <c r="S109" s="6"/>
-      <c r="T109" s="6"/>
-      <c r="U109" s="6"/>
-      <c r="V109" s="6"/>
-      <c r="W109" s="6"/>
-      <c r="X109" s="8"/>
-      <c r="Y109" s="6"/>
-      <c r="Z109" s="6"/>
-      <c r="AA109" s="8"/>
-      <c r="AB109" s="8"/>
-      <c r="AC109" s="8"/>
-      <c r="AD109" s="8"/>
-      <c r="AE109" s="6"/>
+      <c r="O109" s="5">
+        <v>11351.549999999999</v>
+      </c>
+      <c r="P109" s="5">
+        <v>11351.549999999999</v>
+      </c>
+      <c r="Q109" s="6">
+        <v>-0.091503879989243586</v>
+      </c>
+      <c r="R109" s="7">
+        <v>118</v>
+      </c>
+      <c r="S109" s="6">
+        <v>-0.17482517482517479</v>
+      </c>
+      <c r="T109" s="6">
+        <v>0.0064132211019640494</v>
+      </c>
+      <c r="U109" s="6">
+        <v>-0.33282679457871395</v>
+      </c>
+      <c r="V109" s="6">
+        <v>0.050619871295109482</v>
+      </c>
+      <c r="W109" s="6">
+        <v>0.030636697191132489</v>
+      </c>
+      <c r="X109" s="8">
+        <v>25.064491304347825</v>
+      </c>
+      <c r="Y109" s="6">
+        <v>0.39130434782608697</v>
+      </c>
+      <c r="Z109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA109" s="8">
+        <v>4.5877495726495727</v>
+      </c>
+      <c r="AB109" s="8">
+        <v>7.9847826086956522</v>
+      </c>
+      <c r="AC109" s="8">
+        <v>12.171013</v>
+      </c>
+      <c r="AD109" s="8">
+        <v>20.088404347826089</v>
+      </c>
+      <c r="AE109" s="6">
+        <v>0.78260869565217395</v>
+      </c>
       <c r="AF109" s="9"/>
-      <c r="AG109" s="5"/>
+      <c r="AG109" s="5">
+        <v>0</v>
+      </c>
       <c r="AH109" s="10">
         <v>2</v>
       </c>
@@ -14488,7 +15259,9 @@
       <c r="AB111" s="8">
         <v>1.0618041666666667</v>
       </c>
-      <c r="AC111" s="8"/>
+      <c r="AC111" s="8">
+        <v>10.369804999999999</v>
+      </c>
       <c r="AD111" s="8">
         <v>17.198</v>
       </c>
@@ -14708,7 +15481,9 @@
       <c r="AB113" s="8">
         <v>4.5070837500000005</v>
       </c>
-      <c r="AC113" s="8"/>
+      <c r="AC113" s="8">
+        <v>6.4672020000000003</v>
+      </c>
       <c r="AD113" s="8">
         <v>16.267695061728393</v>
       </c>
@@ -14837,7 +15612,9 @@
       <c r="AB114" s="8">
         <v>1.9555549999999999</v>
       </c>
-      <c r="AC114" s="8"/>
+      <c r="AC114" s="8">
+        <v>4.1065649999999998</v>
+      </c>
       <c r="AD114" s="8">
         <v>11.870900000000001</v>
       </c>
@@ -14966,7 +15743,9 @@
       <c r="AB115" s="8">
         <v>3.6892483870967738</v>
       </c>
-      <c r="AC115" s="8"/>
+      <c r="AC115" s="8">
+        <v>6.3252680000000003</v>
+      </c>
       <c r="AD115" s="8">
         <v>14.276345161290324</v>
       </c>
@@ -15188,7 +15967,9 @@
       <c r="AB117" s="8">
         <v>5.5694444444444446</v>
       </c>
-      <c r="AC117" s="8"/>
+      <c r="AC117" s="8">
+        <v>11.119005</v>
+      </c>
       <c r="AD117" s="8">
         <v>17.882432432432431</v>
       </c>
@@ -15239,7 +16020,7 @@
         <v>19746</v>
       </c>
       <c r="B118" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C118" s="4">
         <v>44</v>
@@ -15275,25 +16056,61 @@
       <c t="s" r="N118" s="4">
         <v>52</v>
       </c>
-      <c r="O118" s="5"/>
-      <c r="P118" s="5"/>
-      <c r="Q118" s="6"/>
-      <c r="R118" s="7"/>
-      <c r="S118" s="6"/>
-      <c r="T118" s="6"/>
-      <c r="U118" s="6"/>
-      <c r="V118" s="6"/>
-      <c r="W118" s="6"/>
-      <c r="X118" s="8"/>
-      <c r="Y118" s="6"/>
-      <c r="Z118" s="6"/>
-      <c r="AA118" s="8"/>
-      <c r="AB118" s="8"/>
-      <c r="AC118" s="8"/>
-      <c r="AD118" s="8"/>
-      <c r="AE118" s="6"/>
+      <c r="O118" s="5">
+        <v>11412.969999999999</v>
+      </c>
+      <c r="P118" s="5">
+        <v>11412.969999999999</v>
+      </c>
+      <c r="Q118" s="6">
+        <v>0.029780057963063822</v>
+      </c>
+      <c r="R118" s="7">
+        <v>141</v>
+      </c>
+      <c r="S118" s="6">
+        <v>-0.12962962962962965</v>
+      </c>
+      <c r="T118" s="6">
+        <v>0.39582141195499509</v>
+      </c>
+      <c r="U118" s="6">
+        <v>0.047948772317810348</v>
+      </c>
+      <c r="V118" s="6">
+        <v>0.02257168817582102</v>
+      </c>
+      <c r="W118" s="6">
+        <v>0.0031639441792977638</v>
+      </c>
+      <c r="X118" s="8">
+        <v>29.32950819672131</v>
+      </c>
+      <c r="Y118" s="6">
+        <v>0.32786885245901637</v>
+      </c>
+      <c r="Z118" s="6">
+        <v>0.19672131147540983</v>
+      </c>
+      <c r="AA118" s="8">
+        <v>7.3278225806451607</v>
+      </c>
+      <c r="AB118" s="8">
+        <v>12.930408771929825</v>
+      </c>
+      <c r="AC118" s="8">
+        <v>20.435873000000001</v>
+      </c>
+      <c r="AD118" s="8">
+        <v>26.303824590163934</v>
+      </c>
+      <c r="AE118" s="6">
+        <v>0.63934426229508201</v>
+      </c>
       <c r="AF118" s="9"/>
-      <c r="AG118" s="5"/>
+      <c r="AG118" s="5">
+        <v>-411.89999999999998</v>
+      </c>
       <c r="AH118" s="10">
         <v>2</v>
       </c>
@@ -15412,7 +16229,9 @@
       <c r="AB119" s="8">
         <v>4.338485454545455</v>
       </c>
-      <c r="AC119" s="8"/>
+      <c r="AC119" s="8">
+        <v>8.1387870000000007</v>
+      </c>
       <c r="AD119" s="8">
         <v>15.086363636363636</v>
       </c>
@@ -15539,7 +16358,9 @@
       <c r="AB120" s="8">
         <v>8.7623799999999985</v>
       </c>
-      <c r="AC120" s="8"/>
+      <c r="AC120" s="8">
+        <v>16.506523999999999</v>
+      </c>
       <c r="AD120" s="8">
         <v>23.89144054054054</v>
       </c>
@@ -15666,7 +16487,9 @@
       <c r="AB121" s="8">
         <v>4.8516268292682927</v>
       </c>
-      <c r="AC121" s="8"/>
+      <c r="AC121" s="8">
+        <v>10.175832</v>
+      </c>
       <c r="AD121" s="8">
         <v>17.824207142857144</v>
       </c>
@@ -15717,7 +16540,7 @@
         <v>19753</v>
       </c>
       <c r="B122" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C122" s="4">
         <v>44</v>
@@ -15753,25 +16576,61 @@
       <c t="s" r="N122" s="4">
         <v>52</v>
       </c>
-      <c r="O122" s="5"/>
-      <c r="P122" s="5"/>
-      <c r="Q122" s="6"/>
-      <c r="R122" s="7"/>
-      <c r="S122" s="6"/>
-      <c r="T122" s="6"/>
-      <c r="U122" s="6"/>
-      <c r="V122" s="6"/>
-      <c r="W122" s="6"/>
-      <c r="X122" s="8"/>
-      <c r="Y122" s="6"/>
-      <c r="Z122" s="6"/>
-      <c r="AA122" s="8"/>
-      <c r="AB122" s="8"/>
-      <c r="AC122" s="8"/>
-      <c r="AD122" s="8"/>
-      <c r="AE122" s="6"/>
+      <c r="O122" s="5">
+        <v>8689.6299999999992</v>
+      </c>
+      <c r="P122" s="5">
+        <v>8689.6299999999992</v>
+      </c>
+      <c r="Q122" s="6">
+        <v>0.06798788169287584</v>
+      </c>
+      <c r="R122" s="7">
+        <v>86</v>
+      </c>
+      <c r="S122" s="6">
+        <v>-0.14851485148514854</v>
+      </c>
+      <c r="T122" s="6">
+        <v>0</v>
+      </c>
+      <c r="U122" s="6">
+        <v>-0.299868924223471</v>
+      </c>
+      <c r="V122" s="6">
+        <v>0.046150986865954022</v>
+      </c>
+      <c r="W122" s="6">
+        <v>0.0089790934711834695</v>
+      </c>
+      <c r="X122" s="8">
+        <v>25.589795918367347</v>
+      </c>
+      <c r="Y122" s="6">
+        <v>0.79591836734693877</v>
+      </c>
+      <c r="Z122" s="6">
+        <v>0.10204081632653061</v>
+      </c>
+      <c r="AA122" s="8">
+        <v>3.162744705882353</v>
+      </c>
+      <c r="AB122" s="8">
+        <v>4.3993204081632653</v>
+      </c>
+      <c r="AC122" s="8">
+        <v>7.5867329999999997</v>
+      </c>
+      <c r="AD122" s="8">
+        <v>14.524830612244896</v>
+      </c>
+      <c r="AE122" s="6">
+        <v>0.7142857142857143</v>
+      </c>
       <c r="AF122" s="9"/>
-      <c r="AG122" s="5"/>
+      <c r="AG122" s="5">
+        <v>-157.59999999999999</v>
+      </c>
       <c r="AH122" s="10">
         <v>4</v>
       </c>
@@ -15890,7 +16749,9 @@
       <c r="AB123" s="8">
         <v>4.492423636363637</v>
       </c>
-      <c r="AC123" s="8"/>
+      <c r="AC123" s="8">
+        <v>7.0433329999999996</v>
+      </c>
       <c r="AD123" s="8">
         <v>14.997272727272728</v>
       </c>
@@ -16015,7 +16876,9 @@
       <c r="AB124" s="8">
         <v>14.437038888888887</v>
       </c>
-      <c r="AC124" s="8"/>
+      <c r="AC124" s="8">
+        <v>24.854496999999999</v>
+      </c>
       <c r="AD124" s="8">
         <v>31.498247368421051</v>
       </c>
@@ -16144,7 +17007,9 @@
       <c r="AB125" s="8">
         <v>4.7766666666666673</v>
       </c>
-      <c r="AC125" s="8"/>
+      <c r="AC125" s="8">
+        <v>8.6690900000000006</v>
+      </c>
       <c r="AD125" s="8">
         <v>15.847978787878787</v>
       </c>
@@ -16195,7 +17060,7 @@
         <v>19759</v>
       </c>
       <c r="B126" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C126" s="4">
         <v>44</v>
@@ -16231,25 +17096,57 @@
       <c t="s" r="N126" s="4">
         <v>52</v>
       </c>
-      <c r="O126" s="5"/>
-      <c r="P126" s="5"/>
+      <c r="O126" s="5">
+        <v>3197.6599999999999</v>
+      </c>
+      <c r="P126" s="5">
+        <v>3197.6599999999999</v>
+      </c>
       <c r="Q126" s="6"/>
-      <c r="R126" s="7"/>
+      <c r="R126" s="7">
+        <v>42</v>
+      </c>
       <c r="S126" s="6"/>
-      <c r="T126" s="6"/>
-      <c r="U126" s="6"/>
-      <c r="V126" s="6"/>
-      <c r="W126" s="6"/>
-      <c r="X126" s="8"/>
-      <c r="Y126" s="6"/>
-      <c r="Z126" s="6"/>
-      <c r="AA126" s="8"/>
-      <c r="AB126" s="8"/>
-      <c r="AC126" s="8"/>
-      <c r="AD126" s="8"/>
-      <c r="AE126" s="6"/>
+      <c r="T126" s="6">
+        <v>0.0001313460467967201</v>
+      </c>
+      <c r="U126" s="6">
+        <v>-0.22440784823902482</v>
+      </c>
+      <c r="V126" s="6">
+        <v>0.13823514695120809</v>
+      </c>
+      <c r="W126" s="6">
+        <v>0.12115077900714899</v>
+      </c>
+      <c r="X126" s="8">
+        <v>48.951612903225808</v>
+      </c>
+      <c r="Y126" s="6">
+        <v>0.16129032258064516</v>
+      </c>
+      <c r="Z126" s="6">
+        <v>0.70967741935483875</v>
+      </c>
+      <c r="AA126" s="8">
+        <v>5.931745238095238</v>
+      </c>
+      <c r="AB126" s="8">
+        <v>17.807525806451615</v>
+      </c>
+      <c r="AC126" s="8">
+        <v>23.345697999999999</v>
+      </c>
+      <c r="AD126" s="8">
+        <v>30.265590322580646</v>
+      </c>
+      <c r="AE126" s="6">
+        <v>0.096774193548387094</v>
+      </c>
       <c r="AF126" s="9"/>
-      <c r="AG126" s="5"/>
+      <c r="AG126" s="5">
+        <v>0</v>
+      </c>
       <c r="AH126" s="10">
         <v>2</v>
       </c>
@@ -16368,7 +17265,9 @@
       <c r="AB127" s="8">
         <v>5.6086679999999998</v>
       </c>
-      <c r="AC127" s="8"/>
+      <c r="AC127" s="8">
+        <v>13.622127000000001</v>
+      </c>
       <c r="AD127" s="8">
         <v>23.656668</v>
       </c>
@@ -16497,7 +17396,9 @@
       <c r="AB128" s="8">
         <v>21.138636363636365</v>
       </c>
-      <c r="AC128" s="8"/>
+      <c r="AC128" s="8">
+        <v>32.975440999999996</v>
+      </c>
       <c r="AD128" s="8">
         <v>31.095652173913045</v>
       </c>
@@ -16626,7 +17527,9 @@
       <c r="AB129" s="8">
         <v>12.031559574468085</v>
       </c>
-      <c r="AC129" s="8"/>
+      <c r="AC129" s="8">
+        <v>17.576892999999998</v>
+      </c>
       <c r="AD129" s="8">
         <v>23.794557142857141</v>
       </c>
@@ -16755,7 +17658,9 @@
       <c r="AB130" s="8">
         <v>5.9892857142857148</v>
       </c>
-      <c r="AC130" s="8"/>
+      <c r="AC130" s="8">
+        <v>10.31883</v>
+      </c>
       <c r="AD130" s="8">
         <v>16.710606818181819</v>
       </c>
@@ -16806,7 +17711,7 @@
         <v>19772</v>
       </c>
       <c r="B131" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C131" s="4">
         <v>44</v>
@@ -16842,25 +17747,59 @@
       <c t="s" r="N131" s="4">
         <v>52</v>
       </c>
-      <c r="O131" s="5"/>
-      <c r="P131" s="5"/>
-      <c r="Q131" s="6"/>
-      <c r="R131" s="7"/>
-      <c r="S131" s="6"/>
-      <c r="T131" s="6"/>
-      <c r="U131" s="6"/>
-      <c r="V131" s="6"/>
-      <c r="W131" s="6"/>
-      <c r="X131" s="8"/>
-      <c r="Y131" s="6"/>
+      <c r="O131" s="5">
+        <v>7064.2299999999996</v>
+      </c>
+      <c r="P131" s="5">
+        <v>7064.2299999999996</v>
+      </c>
+      <c r="Q131" s="6">
+        <v>-0.047985930487985717</v>
+      </c>
+      <c r="R131" s="7">
+        <v>66</v>
+      </c>
+      <c r="S131" s="6">
+        <v>-0.13157894736842102</v>
+      </c>
+      <c r="T131" s="6">
+        <v>0</v>
+      </c>
+      <c r="U131" s="6">
+        <v>-0.27802322404564972</v>
+      </c>
+      <c r="V131" s="6">
+        <v>0.063652372586962769</v>
+      </c>
+      <c r="W131" s="6">
+        <v>0.058057990750584286</v>
+      </c>
+      <c r="X131" s="8">
+        <v>39.635000000000005</v>
+      </c>
+      <c r="Y131" s="6">
+        <v>0.75</v>
+      </c>
       <c r="Z131" s="6"/>
-      <c r="AA131" s="8"/>
-      <c r="AB131" s="8"/>
-      <c r="AC131" s="8"/>
-      <c r="AD131" s="8"/>
-      <c r="AE131" s="6"/>
+      <c r="AA131" s="8">
+        <v>8.627874137931034</v>
+      </c>
+      <c r="AB131" s="8">
+        <v>14.847368421052632</v>
+      </c>
+      <c r="AC131" s="8">
+        <v>23.613201</v>
+      </c>
+      <c r="AD131" s="8">
+        <v>29.751665000000003</v>
+      </c>
+      <c r="AE131" s="6">
+        <v>0.20000000000000001</v>
+      </c>
       <c r="AF131" s="9"/>
-      <c r="AG131" s="5"/>
+      <c r="AG131" s="5">
+        <v>-474.80000000000001</v>
+      </c>
       <c r="AH131" s="10">
         <v>0</v>
       </c>
@@ -16979,7 +17918,9 @@
       <c r="AB132" s="8">
         <v>7.1080576158940403</v>
       </c>
-      <c r="AC132" s="8"/>
+      <c r="AC132" s="8">
+        <v>13.117611</v>
+      </c>
       <c r="AD132" s="8">
         <v>18.699785161290322</v>
       </c>
@@ -17108,7 +18049,9 @@
       <c r="AB133" s="8">
         <v>11.111112121212122</v>
       </c>
-      <c r="AC133" s="8"/>
+      <c r="AC133" s="8">
+        <v>20.688095000000001</v>
+      </c>
       <c r="AD133" s="8">
         <v>24.684582499999998</v>
       </c>
@@ -17237,7 +18180,9 @@
       <c r="AB134" s="8">
         <v>23.821796153846154</v>
       </c>
-      <c r="AC134" s="8"/>
+      <c r="AC134" s="8">
+        <v>42.181669999999997</v>
+      </c>
       <c r="AD134" s="8">
         <v>48.308640740740742</v>
       </c>
@@ -17366,7 +18311,9 @@
       <c r="AB135" s="8">
         <v>2.79583125</v>
       </c>
-      <c r="AC135" s="8"/>
+      <c r="AC135" s="8">
+        <v>5.8489579999999997</v>
+      </c>
       <c r="AD135" s="8">
         <v>12.80833125</v>
       </c>
@@ -17588,7 +18535,9 @@
       <c r="AB137" s="8">
         <v>4.7294117647058824</v>
       </c>
-      <c r="AC137" s="8"/>
+      <c r="AC137" s="8">
+        <v>10.930287999999999</v>
+      </c>
       <c r="AD137" s="8">
         <v>17.88529411764706</v>
       </c>
@@ -17715,7 +18664,9 @@
       <c r="AB138" s="8">
         <v>9.5315701923076936</v>
       </c>
-      <c r="AC138" s="8"/>
+      <c r="AC138" s="8">
+        <v>16.627124999999999</v>
+      </c>
       <c r="AD138" s="8">
         <v>21.943600892857145</v>
       </c>
@@ -17844,7 +18795,9 @@
       <c r="AB139" s="8">
         <v>3.5886792452830187</v>
       </c>
-      <c r="AC139" s="8"/>
+      <c r="AC139" s="8">
+        <v>7.9408000000000003</v>
+      </c>
       <c r="AD139" s="8">
         <v>14.646912962962963</v>
       </c>
@@ -18085,7 +19038,7 @@
         <v>19794</v>
       </c>
       <c r="B142" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C142" s="4">
         <v>44</v>
@@ -18119,25 +19072,61 @@
       <c t="s" r="N142" s="4">
         <v>52</v>
       </c>
-      <c r="O142" s="5"/>
-      <c r="P142" s="5"/>
-      <c r="Q142" s="6"/>
-      <c r="R142" s="7"/>
-      <c r="S142" s="6"/>
-      <c r="T142" s="6"/>
-      <c r="U142" s="6"/>
-      <c r="V142" s="6"/>
-      <c r="W142" s="6"/>
-      <c r="X142" s="8"/>
-      <c r="Y142" s="6"/>
-      <c r="Z142" s="6"/>
-      <c r="AA142" s="8"/>
-      <c r="AB142" s="8"/>
-      <c r="AC142" s="8"/>
-      <c r="AD142" s="8"/>
-      <c r="AE142" s="6"/>
+      <c r="O142" s="5">
+        <v>12407.780000000001</v>
+      </c>
+      <c r="P142" s="5">
+        <v>12407.780000000001</v>
+      </c>
+      <c r="Q142" s="6">
+        <v>-0.17599258858336342</v>
+      </c>
+      <c r="R142" s="7">
+        <v>127</v>
+      </c>
+      <c r="S142" s="6">
+        <v>-0.19108280254777066</v>
+      </c>
+      <c r="T142" s="6">
+        <v>0</v>
+      </c>
+      <c r="U142" s="6">
+        <v>-0.34791799983558702</v>
+      </c>
+      <c r="V142" s="6">
+        <v>0.026011623352444998</v>
+      </c>
+      <c r="W142" s="6">
+        <v>0.0072475898186460429</v>
+      </c>
+      <c r="X142" s="8">
+        <v>25.747222916666669</v>
+      </c>
+      <c r="Y142" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="Z142" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA142" s="8">
+        <v>5.6509046511627901</v>
+      </c>
+      <c r="AB142" s="8">
+        <v>6.1142354166666664</v>
+      </c>
+      <c r="AC142" s="8">
+        <v>11.428819000000001</v>
+      </c>
+      <c r="AD142" s="8">
+        <v>20.245139583333334</v>
+      </c>
+      <c r="AE142" s="6">
+        <v>0.77083333333333337</v>
+      </c>
       <c r="AF142" s="9"/>
-      <c r="AG142" s="5"/>
+      <c r="AG142" s="5">
+        <v>0</v>
+      </c>
       <c r="AH142" s="10">
         <v>2</v>
       </c>
@@ -18254,7 +19243,9 @@
       <c r="AB143" s="8">
         <v>9.2788365079365072</v>
       </c>
-      <c r="AC143" s="8"/>
+      <c r="AC143" s="8">
+        <v>16.086663000000001</v>
+      </c>
       <c r="AD143" s="8">
         <v>23.579687499999999</v>
       </c>
@@ -18383,7 +19374,9 @@
       <c r="AB144" s="8">
         <v>3.2930820754716983</v>
       </c>
-      <c r="AC144" s="8"/>
+      <c r="AC144" s="8">
+        <v>6.6381069999999998</v>
+      </c>
       <c r="AD144" s="8">
         <v>13.355757272727272</v>
       </c>
@@ -18512,7 +19505,9 @@
       <c r="AB145" s="8">
         <v>4.4739562499999996</v>
       </c>
-      <c r="AC145" s="8"/>
+      <c r="AC145" s="8">
+        <v>13.019306</v>
+      </c>
       <c r="AD145" s="8">
         <v>14.249611627906976</v>
       </c>
@@ -18641,7 +19636,9 @@
       <c r="AB146" s="8">
         <v>7.2514705882352946</v>
       </c>
-      <c r="AC146" s="8"/>
+      <c r="AC146" s="8">
+        <v>18.798373999999999</v>
+      </c>
       <c r="AD146" s="8">
         <v>24.71348088235294</v>
       </c>
@@ -18770,7 +19767,9 @@
       <c r="AB147" s="8">
         <v>1.7219704545454546</v>
       </c>
-      <c r="AC147" s="8"/>
+      <c r="AC147" s="8">
+        <v>3.8867409999999998</v>
+      </c>
       <c r="AD147" s="8">
         <v>10.840909090909092</v>
       </c>
@@ -18901,7 +19900,9 @@
       <c r="AB148" s="8">
         <v>8.7115653061224485</v>
       </c>
-      <c r="AC148" s="8"/>
+      <c r="AC148" s="8">
+        <v>17.350307999999998</v>
+      </c>
       <c r="AD148" s="8">
         <v>20.333549350649349</v>
       </c>
@@ -18952,7 +19953,7 @@
         <v>19817</v>
       </c>
       <c r="B149" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C149" s="4">
         <v>44</v>
@@ -18988,25 +19989,61 @@
       <c t="s" r="N149" s="4">
         <v>52</v>
       </c>
-      <c r="O149" s="5"/>
-      <c r="P149" s="5"/>
-      <c r="Q149" s="6"/>
-      <c r="R149" s="7"/>
-      <c r="S149" s="6"/>
-      <c r="T149" s="6"/>
-      <c r="U149" s="6"/>
-      <c r="V149" s="6"/>
-      <c r="W149" s="6"/>
-      <c r="X149" s="8"/>
-      <c r="Y149" s="6"/>
-      <c r="Z149" s="6"/>
-      <c r="AA149" s="8"/>
-      <c r="AB149" s="8"/>
-      <c r="AC149" s="8"/>
-      <c r="AD149" s="8"/>
-      <c r="AE149" s="6"/>
+      <c r="O149" s="5">
+        <v>5850.1700000000001</v>
+      </c>
+      <c r="P149" s="5">
+        <v>5850.1700000000001</v>
+      </c>
+      <c r="Q149" s="6">
+        <v>-0.10549774163855818</v>
+      </c>
+      <c r="R149" s="7">
+        <v>71</v>
+      </c>
+      <c r="S149" s="6">
+        <v>0.044117647058823595</v>
+      </c>
+      <c r="T149" s="6">
+        <v>0.29296844365206481</v>
+      </c>
+      <c r="U149" s="6">
+        <v>-0.032775936425779077</v>
+      </c>
+      <c r="V149" s="6">
+        <v>0.029059668351517989</v>
+      </c>
+      <c r="W149" s="6">
+        <v>-0.019342343897698702</v>
+      </c>
+      <c r="X149" s="8">
+        <v>37.351514545454542</v>
+      </c>
+      <c r="Y149" s="6">
+        <v>0.30909090909090908</v>
+      </c>
+      <c r="Z149" s="6">
+        <v>0.45454545454545453</v>
+      </c>
+      <c r="AA149" s="8">
+        <v>9.2002319444444449</v>
+      </c>
+      <c r="AB149" s="8">
+        <v>15.056288679245283</v>
+      </c>
+      <c r="AC149" s="8">
+        <v>25.108830999999999</v>
+      </c>
+      <c r="AD149" s="8">
+        <v>31.194241818181816</v>
+      </c>
+      <c r="AE149" s="6">
+        <v>0.40000000000000002</v>
+      </c>
       <c r="AF149" s="9"/>
-      <c r="AG149" s="5"/>
+      <c r="AG149" s="5">
+        <v>-134.40000000000001</v>
+      </c>
       <c r="AH149" s="10">
         <v>2</v>
       </c>
@@ -19123,7 +20160,9 @@
       <c r="AB150" s="8">
         <v>4.1517102564102562</v>
       </c>
-      <c r="AC150" s="8"/>
+      <c r="AC150" s="8">
+        <v>11.561557000000001</v>
+      </c>
       <c r="AD150" s="8">
         <v>17.700756818181819</v>
       </c>
@@ -19351,7 +20390,9 @@
       <c r="AB152" s="8">
         <v>4.0838085714285715</v>
       </c>
-      <c r="AC152" s="8"/>
+      <c r="AC152" s="8">
+        <v>8.8356600000000007</v>
+      </c>
       <c r="AD152" s="8">
         <v>15.572686111111112</v>
       </c>
@@ -19480,7 +20521,9 @@
       <c r="AB153" s="8">
         <v>7.75</v>
       </c>
-      <c r="AC153" s="8"/>
+      <c r="AC153" s="8">
+        <v>12.482340000000001</v>
+      </c>
       <c r="AD153" s="8">
         <v>19.571084337349397</v>
       </c>
@@ -19609,7 +20652,9 @@
       <c r="AB154" s="8">
         <v>13.745036170212765</v>
       </c>
-      <c r="AC154" s="8"/>
+      <c r="AC154" s="8">
+        <v>21.165520999999998</v>
+      </c>
       <c r="AD154" s="8">
         <v>29.791318750000002</v>
       </c>
@@ -19736,7 +20781,9 @@
       <c r="AB155" s="8">
         <v>2.9469344827586208</v>
       </c>
-      <c r="AC155" s="8"/>
+      <c r="AC155" s="8">
+        <v>5.7568950000000001</v>
+      </c>
       <c r="AD155" s="8">
         <v>11.824712643678161</v>
       </c>
@@ -19865,7 +20912,9 @@
       <c r="AB156" s="8">
         <v>5.2826395833333333</v>
       </c>
-      <c r="AC156" s="8"/>
+      <c r="AC156" s="8">
+        <v>9.6853590000000001</v>
+      </c>
       <c r="AD156" s="8">
         <v>16.497568749999999</v>
       </c>
@@ -20156,7 +21205,9 @@
       <c r="Z159" s="6"/>
       <c r="AA159" s="8"/>
       <c r="AB159" s="8"/>
-      <c r="AC159" s="8"/>
+      <c r="AC159" s="8">
+        <v>27.563872</v>
+      </c>
       <c r="AD159" s="8"/>
       <c r="AE159" s="6"/>
       <c r="AF159" s="9"/>
@@ -20199,7 +21250,7 @@
         <v>19866</v>
       </c>
       <c r="B160" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C160" s="4">
         <v>44</v>
@@ -20233,25 +21284,61 @@
       <c t="s" r="N160" s="4">
         <v>52</v>
       </c>
-      <c r="O160" s="5"/>
-      <c r="P160" s="5"/>
-      <c r="Q160" s="6"/>
-      <c r="R160" s="7"/>
-      <c r="S160" s="6"/>
-      <c r="T160" s="6"/>
-      <c r="U160" s="6"/>
-      <c r="V160" s="6"/>
-      <c r="W160" s="6"/>
-      <c r="X160" s="8"/>
-      <c r="Y160" s="6"/>
-      <c r="Z160" s="6"/>
-      <c r="AA160" s="8"/>
-      <c r="AB160" s="8"/>
-      <c r="AC160" s="8"/>
-      <c r="AD160" s="8"/>
-      <c r="AE160" s="6"/>
+      <c r="O160" s="5">
+        <v>6132.3500000000004</v>
+      </c>
+      <c r="P160" s="5">
+        <v>6132.3500000000004</v>
+      </c>
+      <c r="Q160" s="6">
+        <v>-0.19770603072929749</v>
+      </c>
+      <c r="R160" s="7">
+        <v>63</v>
+      </c>
+      <c r="S160" s="6">
+        <v>-0.22222222222222221</v>
+      </c>
+      <c r="T160" s="6">
+        <v>0.32144515560918729</v>
+      </c>
+      <c r="U160" s="6">
+        <v>0.00087147667696723112</v>
+      </c>
+      <c r="V160" s="6">
+        <v>0.077029768359601125</v>
+      </c>
+      <c r="W160" s="6">
+        <v>0.026792909732810424</v>
+      </c>
+      <c r="X160" s="8">
+        <v>59.874849090909095</v>
+      </c>
+      <c r="Y160" s="6">
+        <v>0.14545454545454545</v>
+      </c>
+      <c r="Z160" s="6">
+        <v>0.70909090909090911</v>
+      </c>
+      <c r="AA160" s="8">
+        <v>15.844531249999999</v>
+      </c>
+      <c r="AB160" s="8">
+        <v>21.783636363636361</v>
+      </c>
+      <c r="AC160" s="8">
+        <v>39.423029</v>
+      </c>
+      <c r="AD160" s="8">
+        <v>46.331212727272728</v>
+      </c>
+      <c r="AE160" s="6">
+        <v>0.018181818181818181</v>
+      </c>
       <c r="AF160" s="9"/>
-      <c r="AG160" s="5"/>
+      <c r="AG160" s="5">
+        <v>-94.400000000000006</v>
+      </c>
       <c r="AH160" s="10">
         <v>2</v>
       </c>
@@ -20290,7 +21377,7 @@
         <v>19868</v>
       </c>
       <c r="B161" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C161" s="4">
         <v>44</v>
@@ -20326,25 +21413,47 @@
       <c t="s" r="N161" s="4">
         <v>52</v>
       </c>
-      <c r="O161" s="5"/>
-      <c r="P161" s="5"/>
-      <c r="Q161" s="6"/>
-      <c r="R161" s="7"/>
-      <c r="S161" s="6"/>
-      <c r="T161" s="6"/>
-      <c r="U161" s="6"/>
-      <c r="V161" s="6"/>
-      <c r="W161" s="6"/>
+      <c r="O161" s="5">
+        <v>10487.4</v>
+      </c>
+      <c r="P161" s="5">
+        <v>10487.4</v>
+      </c>
+      <c r="Q161" s="6">
+        <v>-0.1673097994378544</v>
+      </c>
+      <c r="R161" s="7">
+        <v>128</v>
+      </c>
+      <c r="S161" s="6">
+        <v>-0.22424242424242424</v>
+      </c>
+      <c r="T161" s="6">
+        <v>-0.01539943169899117</v>
+      </c>
+      <c r="U161" s="6">
+        <v>-0.33216049735873526</v>
+      </c>
+      <c r="V161" s="6">
+        <v>0.012108959322615711</v>
+      </c>
+      <c r="W161" s="6">
+        <v>-0.0026048877700860082</v>
+      </c>
       <c r="X161" s="8"/>
       <c r="Y161" s="6"/>
       <c r="Z161" s="6"/>
-      <c r="AA161" s="8"/>
+      <c r="AA161" s="8">
+        <v>14.736637931034483</v>
+      </c>
       <c r="AB161" s="8"/>
       <c r="AC161" s="8"/>
       <c r="AD161" s="8"/>
       <c r="AE161" s="6"/>
       <c r="AF161" s="9"/>
-      <c r="AG161" s="5"/>
+      <c r="AG161" s="5">
+        <v>-1999.0999999999999</v>
+      </c>
       <c r="AH161" s="10">
         <v>5</v>
       </c>
@@ -20385,7 +21494,7 @@
         <v>19872</v>
       </c>
       <c r="B162" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C162" s="4">
         <v>44</v>
@@ -20421,25 +21530,61 @@
       <c t="s" r="N162" s="4">
         <v>52</v>
       </c>
-      <c r="O162" s="5"/>
-      <c r="P162" s="5"/>
-      <c r="Q162" s="6"/>
-      <c r="R162" s="7"/>
-      <c r="S162" s="6"/>
-      <c r="T162" s="6"/>
-      <c r="U162" s="6"/>
-      <c r="V162" s="6"/>
-      <c r="W162" s="6"/>
-      <c r="X162" s="8"/>
-      <c r="Y162" s="6"/>
-      <c r="Z162" s="6"/>
-      <c r="AA162" s="8"/>
-      <c r="AB162" s="8"/>
-      <c r="AC162" s="8"/>
-      <c r="AD162" s="8"/>
-      <c r="AE162" s="6"/>
+      <c r="O162" s="5">
+        <v>17810.689999999999</v>
+      </c>
+      <c r="P162" s="5">
+        <v>17810.689999999999</v>
+      </c>
+      <c r="Q162" s="6">
+        <v>0.34428824166966043</v>
+      </c>
+      <c r="R162" s="7">
+        <v>162</v>
+      </c>
+      <c r="S162" s="6">
+        <v>0.06578947368421062</v>
+      </c>
+      <c r="T162" s="6">
+        <v>0.27251015541789791</v>
+      </c>
+      <c r="U162" s="6">
+        <v>0.012350666930927437</v>
+      </c>
+      <c r="V162" s="6">
+        <v>0.029494112805287166</v>
+      </c>
+      <c r="W162" s="6">
+        <v>0.023342750898477264</v>
+      </c>
+      <c r="X162" s="8">
+        <v>46.679227536231885</v>
+      </c>
+      <c r="Y162" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="Z162" s="6">
+        <v>0.49275362318840582</v>
+      </c>
+      <c r="AA162" s="8">
+        <v>25.367221999999998</v>
+      </c>
+      <c r="AB162" s="8">
+        <v>5.074879710144927</v>
+      </c>
+      <c r="AC162" s="8">
+        <v>32.425223000000003</v>
+      </c>
+      <c r="AD162" s="8">
+        <v>40.500242028985511</v>
+      </c>
+      <c r="AE162" s="6">
+        <v>0.14492753623188406</v>
+      </c>
       <c r="AF162" s="9"/>
-      <c r="AG162" s="5"/>
+      <c r="AG162" s="5">
+        <v>-447.5</v>
+      </c>
       <c r="AH162" s="10">
         <v>2</v>
       </c>
@@ -20558,7 +21703,9 @@
       <c r="AB163" s="8">
         <v>6.3818522222222223</v>
       </c>
-      <c r="AC163" s="8"/>
+      <c r="AC163" s="8">
+        <v>9.9748330000000003</v>
+      </c>
       <c r="AD163" s="8">
         <v>17.088194791666666</v>
       </c>
@@ -20687,7 +21834,9 @@
       <c r="AB164" s="8">
         <v>5.6596491228070178</v>
       </c>
-      <c r="AC164" s="8"/>
+      <c r="AC164" s="8">
+        <v>17.149512999999999</v>
+      </c>
       <c r="AD164" s="8">
         <v>22.070422535211268</v>
       </c>
@@ -20833,7 +21982,7 @@
         <v>19879</v>
       </c>
       <c r="B166" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C166" s="4">
         <v>44</v>
@@ -20869,25 +22018,61 @@
       <c t="s" r="N166" s="4">
         <v>52</v>
       </c>
-      <c r="O166" s="5"/>
-      <c r="P166" s="5"/>
-      <c r="Q166" s="6"/>
-      <c r="R166" s="7"/>
-      <c r="S166" s="6"/>
-      <c r="T166" s="6"/>
-      <c r="U166" s="6"/>
-      <c r="V166" s="6"/>
-      <c r="W166" s="6"/>
-      <c r="X166" s="8"/>
-      <c r="Y166" s="6"/>
-      <c r="Z166" s="6"/>
-      <c r="AA166" s="8"/>
-      <c r="AB166" s="8"/>
-      <c r="AC166" s="8"/>
-      <c r="AD166" s="8"/>
-      <c r="AE166" s="6"/>
+      <c r="O166" s="5">
+        <v>10885.280000000001</v>
+      </c>
+      <c r="P166" s="5">
+        <v>10885.280000000001</v>
+      </c>
+      <c r="Q166" s="6">
+        <v>-0.15077641302176947</v>
+      </c>
+      <c r="R166" s="7">
+        <v>94</v>
+      </c>
+      <c r="S166" s="6">
+        <v>-0.1607142857142857</v>
+      </c>
+      <c r="T166" s="6">
+        <v>0.2373306704099481</v>
+      </c>
+      <c r="U166" s="6">
+        <v>-0.048851219261240864</v>
+      </c>
+      <c r="V166" s="6">
+        <v>0.038531852189378685</v>
+      </c>
+      <c r="W166" s="6">
+        <v>0.025453640145223638</v>
+      </c>
+      <c r="X166" s="8">
+        <v>27.991472093023255</v>
+      </c>
+      <c r="Y166" s="6">
+        <v>0.18604651162790697</v>
+      </c>
+      <c r="Z166" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA166" s="8">
+        <v>4.8143943181818178</v>
+      </c>
+      <c r="AB166" s="8">
+        <v>9.6542627906976755</v>
+      </c>
+      <c r="AC166" s="8">
+        <v>14.216564</v>
+      </c>
+      <c r="AD166" s="8">
+        <v>21.022093023255817</v>
+      </c>
+      <c r="AE166" s="6">
+        <v>0.67441860465116277</v>
+      </c>
       <c r="AF166" s="9"/>
-      <c r="AG166" s="5"/>
+      <c r="AG166" s="5">
+        <v>-573.89999999999998</v>
+      </c>
       <c r="AH166" s="10">
         <v>3</v>
       </c>
@@ -21006,7 +22191,9 @@
       <c r="AB167" s="8">
         <v>7.4425089887640441</v>
       </c>
-      <c r="AC167" s="8"/>
+      <c r="AC167" s="8">
+        <v>9.8819529999999993</v>
+      </c>
       <c r="AD167" s="8">
         <v>16.044444444444444</v>
       </c>
@@ -21135,7 +22322,9 @@
       <c r="AB168" s="8">
         <v>4.9463414634146341</v>
       </c>
-      <c r="AC168" s="8"/>
+      <c r="AC168" s="8">
+        <v>8.5097550000000002</v>
+      </c>
       <c r="AD168" s="8">
         <v>15.421139024390245</v>
       </c>
@@ -21186,7 +22375,7 @@
         <v>19884</v>
       </c>
       <c r="B169" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C169" s="4">
         <v>44</v>
@@ -21222,25 +22411,61 @@
       <c t="s" r="N169" s="4">
         <v>52</v>
       </c>
-      <c r="O169" s="5"/>
-      <c r="P169" s="5"/>
-      <c r="Q169" s="6"/>
-      <c r="R169" s="7"/>
-      <c r="S169" s="6"/>
-      <c r="T169" s="6"/>
-      <c r="U169" s="6"/>
-      <c r="V169" s="6"/>
-      <c r="W169" s="6"/>
-      <c r="X169" s="8"/>
-      <c r="Y169" s="6"/>
-      <c r="Z169" s="6"/>
-      <c r="AA169" s="8"/>
-      <c r="AB169" s="8"/>
-      <c r="AC169" s="8"/>
-      <c r="AD169" s="8"/>
-      <c r="AE169" s="6"/>
+      <c r="O169" s="5">
+        <v>5123.0699999999997</v>
+      </c>
+      <c r="P169" s="5">
+        <v>5123.0699999999997</v>
+      </c>
+      <c r="Q169" s="6">
+        <v>-0.41240639405050961</v>
+      </c>
+      <c r="R169" s="7">
+        <v>52</v>
+      </c>
+      <c r="S169" s="6">
+        <v>-0.45263157894736838</v>
+      </c>
+      <c r="T169" s="6">
+        <v>0.29245345076292145</v>
+      </c>
+      <c r="U169" s="6">
+        <v>0.017467944025750186</v>
+      </c>
+      <c r="V169" s="6">
+        <v>0.022500863739905955</v>
+      </c>
+      <c r="W169" s="6">
+        <v>-0.026128180953998291</v>
+      </c>
+      <c r="X169" s="8">
+        <v>31.152381632653061</v>
+      </c>
+      <c r="Y169" s="6">
+        <v>0.16</v>
+      </c>
+      <c r="Z169" s="6">
+        <v>0.081632653061224483</v>
+      </c>
+      <c r="AA169" s="8">
+        <v>7.0066037735849065</v>
+      </c>
+      <c r="AB169" s="8">
+        <v>6.303173809523809</v>
+      </c>
+      <c r="AC169" s="8">
+        <v>13.315507</v>
+      </c>
+      <c r="AD169" s="8">
+        <v>18.844557142857141</v>
+      </c>
+      <c r="AE169" s="6">
+        <v>0.42857142857142855</v>
+      </c>
       <c r="AF169" s="9"/>
-      <c r="AG169" s="5"/>
+      <c r="AG169" s="5">
+        <v>0</v>
+      </c>
       <c r="AH169" s="10">
         <v>3</v>
       </c>
@@ -21359,7 +22584,9 @@
       <c r="AB170" s="8">
         <v>7.1467741935483877</v>
       </c>
-      <c r="AC170" s="8"/>
+      <c r="AC170" s="8">
+        <v>12.751343</v>
+      </c>
       <c r="AD170" s="8">
         <v>19.677688709677419</v>
       </c>
@@ -21488,7 +22715,9 @@
       <c r="AB171" s="8">
         <v>4.5059754716981129</v>
       </c>
-      <c r="AC171" s="8"/>
+      <c r="AC171" s="8">
+        <v>14.113265</v>
+      </c>
       <c r="AD171" s="8">
         <v>19.702604687499999</v>
       </c>
@@ -21617,7 +22846,9 @@
       <c r="AB172" s="8">
         <v>6.302021212121212</v>
       </c>
-      <c r="AC172" s="8"/>
+      <c r="AC172" s="8">
+        <v>10.769696</v>
+      </c>
       <c r="AD172" s="8">
         <v>17.733333333333334</v>
       </c>
@@ -21746,7 +22977,9 @@
       <c r="AB173" s="8">
         <v>11.276664999999999</v>
       </c>
-      <c r="AC173" s="8"/>
+      <c r="AC173" s="8">
+        <v>16.287330999999998</v>
+      </c>
       <c r="AD173" s="8">
         <v>16.561273529411764</v>
       </c>
@@ -21875,7 +23108,9 @@
       <c r="AB174" s="8">
         <v>3.9838330000000002</v>
       </c>
-      <c r="AC174" s="8"/>
+      <c r="AC174" s="8">
+        <v>11.808016</v>
+      </c>
       <c r="AD174" s="8">
         <v>18.661881188118812</v>
       </c>
@@ -22004,7 +23239,9 @@
       <c r="AB175" s="8">
         <v>4.234285714285714</v>
       </c>
-      <c r="AC175" s="8"/>
+      <c r="AC175" s="8">
+        <v>17.611039000000002</v>
+      </c>
       <c r="AD175" s="8">
         <v>24.121052631578948</v>
       </c>
@@ -22127,7 +23364,9 @@
       <c r="AB176" s="8">
         <v>36.735294117647058</v>
       </c>
-      <c r="AC176" s="8"/>
+      <c r="AC176" s="8">
+        <v>42.427399000000001</v>
+      </c>
       <c r="AD176" s="8">
         <v>49.173529411764711</v>
       </c>
@@ -22256,7 +23495,9 @@
       <c r="AB177" s="8">
         <v>2.0046680000000001</v>
       </c>
-      <c r="AC177" s="8"/>
+      <c r="AC177" s="8">
+        <v>6.1484930000000002</v>
+      </c>
       <c r="AD177" s="8">
         <v>12.838888888888889</v>
       </c>
@@ -22385,7 +23626,9 @@
       <c r="AB178" s="8">
         <v>3.326969090909091</v>
       </c>
-      <c r="AC178" s="8"/>
+      <c r="AC178" s="8">
+        <v>11.610302000000001</v>
+      </c>
       <c r="AD178" s="8">
         <v>18.57303090909091</v>
       </c>
@@ -22512,7 +23755,9 @@
       <c r="AB179" s="8">
         <v>0.85188679245283017</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>5.6301870000000003</v>
+      </c>
       <c r="AD179" s="8">
         <v>12.586477358490566</v>
       </c>
@@ -22561,7 +23806,7 @@
         <v>19908</v>
       </c>
       <c r="B180" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C180" s="4">
         <v>44</v>
@@ -22597,25 +23842,61 @@
       <c t="s" r="N180" s="4">
         <v>52</v>
       </c>
-      <c r="O180" s="5"/>
-      <c r="P180" s="5"/>
-      <c r="Q180" s="6"/>
-      <c r="R180" s="7"/>
-      <c r="S180" s="6"/>
-      <c r="T180" s="6"/>
-      <c r="U180" s="6"/>
-      <c r="V180" s="6"/>
-      <c r="W180" s="6"/>
-      <c r="X180" s="8"/>
-      <c r="Y180" s="6"/>
-      <c r="Z180" s="6"/>
-      <c r="AA180" s="8"/>
-      <c r="AB180" s="8"/>
-      <c r="AC180" s="8"/>
-      <c r="AD180" s="8"/>
-      <c r="AE180" s="6"/>
+      <c r="O180" s="5">
+        <v>8759.5</v>
+      </c>
+      <c r="P180" s="5">
+        <v>8759.5</v>
+      </c>
+      <c r="Q180" s="6">
+        <v>0.58945744873888595</v>
+      </c>
+      <c r="R180" s="7">
+        <v>85</v>
+      </c>
+      <c r="S180" s="6">
+        <v>0.18055555555555558</v>
+      </c>
+      <c r="T180" s="6">
+        <v>0</v>
+      </c>
+      <c r="U180" s="6">
+        <v>-0.30339973742793541</v>
+      </c>
+      <c r="V180" s="6">
+        <v>0.0050218619784234255</v>
+      </c>
+      <c r="W180" s="6">
+        <v>-0.01034659512529254</v>
+      </c>
+      <c r="X180" s="8">
+        <v>50.635857575757576</v>
+      </c>
+      <c r="Y180" s="6">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="Z180" s="6">
+        <v>0.75757575757575757</v>
+      </c>
+      <c r="AA180" s="8">
+        <v>6.572764634146341</v>
+      </c>
+      <c r="AB180" s="8">
+        <v>23.572580645161292</v>
+      </c>
+      <c r="AC180" s="8">
+        <v>30.070619000000001</v>
+      </c>
+      <c r="AD180" s="8">
+        <v>37.160937500000003</v>
+      </c>
+      <c r="AE180" s="6">
+        <v>0.15151515151515152</v>
+      </c>
       <c r="AF180" s="9"/>
-      <c r="AG180" s="5"/>
+      <c r="AG180" s="5">
+        <v>-109.59999999999999</v>
+      </c>
       <c r="AH180" s="10">
         <v>2</v>
       </c>
@@ -22656,7 +23937,7 @@
         <v>19910</v>
       </c>
       <c r="B181" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C181" s="4">
         <v>44</v>
@@ -22692,25 +23973,61 @@
       <c t="s" r="N181" s="4">
         <v>52</v>
       </c>
-      <c r="O181" s="5"/>
-      <c r="P181" s="5"/>
-      <c r="Q181" s="6"/>
-      <c r="R181" s="7"/>
-      <c r="S181" s="6"/>
-      <c r="T181" s="6"/>
-      <c r="U181" s="6"/>
-      <c r="V181" s="6"/>
-      <c r="W181" s="6"/>
-      <c r="X181" s="8"/>
-      <c r="Y181" s="6"/>
-      <c r="Z181" s="6"/>
-      <c r="AA181" s="8"/>
-      <c r="AB181" s="8"/>
-      <c r="AC181" s="8"/>
-      <c r="AD181" s="8"/>
-      <c r="AE181" s="6"/>
+      <c r="O181" s="5">
+        <v>4525.5799999999999</v>
+      </c>
+      <c r="P181" s="5">
+        <v>4525.5799999999999</v>
+      </c>
+      <c r="Q181" s="6">
+        <v>-0.36873893691127624</v>
+      </c>
+      <c r="R181" s="7">
+        <v>43</v>
+      </c>
+      <c r="S181" s="6">
+        <v>-0.45569620253164556</v>
+      </c>
+      <c r="T181" s="6">
+        <v>-0.031708642870085159</v>
+      </c>
+      <c r="U181" s="6">
+        <v>-0.30648447270847051</v>
+      </c>
+      <c r="V181" s="6">
+        <v>0.071996407090361897</v>
+      </c>
+      <c r="W181" s="6">
+        <v>0.046439461903225669</v>
+      </c>
+      <c r="X181" s="8">
+        <v>15.317241379310344</v>
+      </c>
+      <c r="Y181" s="6">
+        <v>0.58620689655172409</v>
+      </c>
+      <c r="Z181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA181" s="8">
+        <v>3.6759697674418605</v>
+      </c>
+      <c r="AB181" s="8">
+        <v>0.41363636363636364</v>
+      </c>
+      <c r="AC181" s="8">
+        <v>4.2386359999999996</v>
+      </c>
+      <c r="AD181" s="8">
+        <v>10.535058620689655</v>
+      </c>
+      <c r="AE181" s="6">
+        <v>1</v>
+      </c>
       <c r="AF181" s="9"/>
-      <c r="AG181" s="5"/>
+      <c r="AG181" s="5">
+        <v>0</v>
+      </c>
       <c r="AH181" s="10">
         <v>3</v>
       </c>
@@ -22829,7 +24146,9 @@
       <c r="AB182" s="8">
         <v>6.6978723404255325</v>
       </c>
-      <c r="AC182" s="8"/>
+      <c r="AC182" s="8">
+        <v>12.559538</v>
+      </c>
       <c r="AD182" s="8">
         <v>18.384462711864405</v>
       </c>
@@ -22958,7 +24277,9 @@
       <c r="AB183" s="8">
         <v>2.9137044444444444</v>
       </c>
-      <c r="AC183" s="8"/>
+      <c r="AC183" s="8">
+        <v>7.4129620000000003</v>
+      </c>
       <c r="AD183" s="8">
         <v>15.355184444444443</v>
       </c>
@@ -23087,7 +24408,9 @@
       <c r="AB184" s="8">
         <v>16.689320388349515</v>
       </c>
-      <c r="AC184" s="8"/>
+      <c r="AC184" s="8">
+        <v>26.265554000000002</v>
+      </c>
       <c r="AD184" s="8">
         <v>34.155400925925925</v>
       </c>
@@ -23309,7 +24632,9 @@
       <c r="AB186" s="8">
         <v>6.2818181818181813</v>
       </c>
-      <c r="AC186" s="8"/>
+      <c r="AC186" s="8">
+        <v>12.148484</v>
+      </c>
       <c r="AD186" s="8">
         <v>18.219445833333335</v>
       </c>
@@ -23535,7 +24860,9 @@
       <c r="AB188" s="8">
         <v>5.0302714285714289</v>
       </c>
-      <c r="AC188" s="8"/>
+      <c r="AC188" s="8">
+        <v>9.2861740000000008</v>
+      </c>
       <c r="AD188" s="8">
         <v>16.166326530612245</v>
       </c>
@@ -23586,7 +24913,7 @@
         <v>19930</v>
       </c>
       <c r="B189" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C189" s="4">
         <v>44</v>
@@ -23622,25 +24949,61 @@
       <c t="s" r="N189" s="4">
         <v>52</v>
       </c>
-      <c r="O189" s="5"/>
-      <c r="P189" s="5"/>
-      <c r="Q189" s="6"/>
-      <c r="R189" s="7"/>
-      <c r="S189" s="6"/>
-      <c r="T189" s="6"/>
-      <c r="U189" s="6"/>
-      <c r="V189" s="6"/>
-      <c r="W189" s="6"/>
-      <c r="X189" s="8"/>
-      <c r="Y189" s="6"/>
-      <c r="Z189" s="6"/>
-      <c r="AA189" s="8"/>
-      <c r="AB189" s="8"/>
-      <c r="AC189" s="8"/>
-      <c r="AD189" s="8"/>
-      <c r="AE189" s="6"/>
+      <c r="O189" s="5">
+        <v>7841.46</v>
+      </c>
+      <c r="P189" s="5">
+        <v>7841.46</v>
+      </c>
+      <c r="Q189" s="6">
+        <v>0.29129395180945106</v>
+      </c>
+      <c r="R189" s="7">
+        <v>123</v>
+      </c>
+      <c r="S189" s="6">
+        <v>0.22999999999999998</v>
+      </c>
+      <c r="T189" s="6">
+        <v>0.28928223825665123</v>
+      </c>
+      <c r="U189" s="6">
+        <v>0.012072381928875489</v>
+      </c>
+      <c r="V189" s="6">
+        <v>0.056495282766219554</v>
+      </c>
+      <c r="W189" s="6">
+        <v>0.032952473136380216</v>
+      </c>
+      <c r="X189" s="8">
+        <v>28.617948717948721</v>
+      </c>
+      <c r="Y189" s="6">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="Z189" s="6">
+        <v>0.13675213675213677</v>
+      </c>
+      <c r="AA189" s="8">
+        <v>3.3943548387096771</v>
+      </c>
+      <c r="AB189" s="8">
+        <v>14.016666363636364</v>
+      </c>
+      <c r="AC189" s="8">
+        <v>17.384187000000001</v>
+      </c>
+      <c r="AD189" s="8">
+        <v>23.172506837606839</v>
+      </c>
+      <c r="AE189" s="6">
+        <v>0.60683760683760679</v>
+      </c>
       <c r="AF189" s="9"/>
-      <c r="AG189" s="5"/>
+      <c r="AG189" s="5">
+        <v>0</v>
+      </c>
       <c r="AH189" s="10">
         <v>3</v>
       </c>
@@ -23681,7 +25044,7 @@
         <v>19931</v>
       </c>
       <c r="B190" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C190" s="4">
         <v>44</v>
@@ -23717,25 +25080,61 @@
       <c t="s" r="N190" s="4">
         <v>52</v>
       </c>
-      <c r="O190" s="5"/>
-      <c r="P190" s="5"/>
-      <c r="Q190" s="6"/>
-      <c r="R190" s="7"/>
-      <c r="S190" s="6"/>
-      <c r="T190" s="6"/>
-      <c r="U190" s="6"/>
-      <c r="V190" s="6"/>
-      <c r="W190" s="6"/>
-      <c r="X190" s="8"/>
-      <c r="Y190" s="6"/>
-      <c r="Z190" s="6"/>
-      <c r="AA190" s="8"/>
-      <c r="AB190" s="8"/>
-      <c r="AC190" s="8"/>
-      <c r="AD190" s="8"/>
-      <c r="AE190" s="6"/>
+      <c r="O190" s="5">
+        <v>10873.41</v>
+      </c>
+      <c r="P190" s="5">
+        <v>10873.41</v>
+      </c>
+      <c r="Q190" s="6">
+        <v>-0.086093733846708598</v>
+      </c>
+      <c r="R190" s="7">
+        <v>110</v>
+      </c>
+      <c r="S190" s="6">
+        <v>-0.1472868217054264</v>
+      </c>
+      <c r="T190" s="6">
+        <v>-15.25099516159144</v>
+      </c>
+      <c r="U190" s="6">
+        <v>-15.540379080711569</v>
+      </c>
+      <c r="V190" s="6">
+        <v>0.047725598501298129</v>
+      </c>
+      <c r="W190" s="6">
+        <v>0.03513065358521384</v>
+      </c>
+      <c r="X190" s="8">
+        <v>38.400739999999999</v>
+      </c>
+      <c r="Y190" s="6">
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="Z190" s="6">
+        <v>0.31111111111111112</v>
+      </c>
+      <c r="AA190" s="8">
+        <v>7.7922952830188681</v>
+      </c>
+      <c r="AB190" s="8">
+        <v>12.316295555555556</v>
+      </c>
+      <c r="AC190" s="8">
+        <v>18.752220999999999</v>
+      </c>
+      <c r="AD190" s="8">
+        <v>25.698148888888888</v>
+      </c>
+      <c r="AE190" s="6">
+        <v>0.44444444444444442</v>
+      </c>
       <c r="AF190" s="9"/>
-      <c r="AG190" s="5"/>
+      <c r="AG190" s="5">
+        <v>-291.30000000000001</v>
+      </c>
       <c r="AH190" s="10">
         <v>2</v>
       </c>
@@ -23850,7 +25249,9 @@
       <c r="AB191" s="8">
         <v>14.072222222222223</v>
       </c>
-      <c r="AC191" s="8"/>
+      <c r="AC191" s="8">
+        <v>22.599999</v>
+      </c>
       <c r="AD191" s="8">
         <v>29.499074999999998</v>
       </c>
@@ -23977,7 +25378,9 @@
       <c r="AB192" s="8">
         <v>15.053030303030303</v>
       </c>
-      <c r="AC192" s="8"/>
+      <c r="AC192" s="8">
+        <v>22.765656</v>
+      </c>
       <c r="AD192" s="8">
         <v>29.704039393939393</v>
       </c>
@@ -24104,7 +25507,9 @@
       <c r="AB193" s="8">
         <v>7.5354166666666664</v>
       </c>
-      <c r="AC193" s="8"/>
+      <c r="AC193" s="8">
+        <v>11.662297000000001</v>
+      </c>
       <c r="AD193" s="8">
         <v>18.135416666666668</v>
       </c>
@@ -24157,7 +25562,7 @@
         <v>19943</v>
       </c>
       <c r="B194" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C194" s="4">
         <v>44</v>
@@ -24193,25 +25598,61 @@
       <c t="s" r="N194" s="4">
         <v>52</v>
       </c>
-      <c r="O194" s="5"/>
-      <c r="P194" s="5"/>
-      <c r="Q194" s="6"/>
-      <c r="R194" s="7"/>
-      <c r="S194" s="6"/>
-      <c r="T194" s="6"/>
-      <c r="U194" s="6"/>
-      <c r="V194" s="6"/>
-      <c r="W194" s="6"/>
-      <c r="X194" s="8"/>
-      <c r="Y194" s="6"/>
-      <c r="Z194" s="6"/>
-      <c r="AA194" s="8"/>
-      <c r="AB194" s="8"/>
-      <c r="AC194" s="8"/>
-      <c r="AD194" s="8"/>
-      <c r="AE194" s="6"/>
+      <c r="O194" s="5">
+        <v>3828.6999999999998</v>
+      </c>
+      <c r="P194" s="5">
+        <v>3828.6999999999998</v>
+      </c>
+      <c r="Q194" s="6">
+        <v>-0.28442736620976572</v>
+      </c>
+      <c r="R194" s="7">
+        <v>47</v>
+      </c>
+      <c r="S194" s="6">
+        <v>-0.20338983050847459</v>
+      </c>
+      <c r="T194" s="6">
+        <v>0.37910557108156823</v>
+      </c>
+      <c r="U194" s="6">
+        <v>0.015358084989683182</v>
+      </c>
+      <c r="V194" s="6">
+        <v>0.17216300571995716</v>
+      </c>
+      <c r="W194" s="6">
+        <v>0.078556820853031062</v>
+      </c>
+      <c r="X194" s="8">
+        <v>24.79195517241379</v>
+      </c>
+      <c r="Y194" s="6">
+        <v>0.75862068965517238</v>
+      </c>
+      <c r="Z194" s="6">
+        <v>0.068965517241379309</v>
+      </c>
+      <c r="AA194" s="8">
+        <v>8.2517354166666674</v>
+      </c>
+      <c r="AB194" s="8">
+        <v>7.2801269230769226</v>
+      </c>
+      <c r="AC194" s="8">
+        <v>15.966334</v>
+      </c>
+      <c r="AD194" s="8">
+        <v>21.675286206896551</v>
+      </c>
+      <c r="AE194" s="6">
+        <v>0.75862068965517238</v>
+      </c>
       <c r="AF194" s="9"/>
-      <c r="AG194" s="5"/>
+      <c r="AG194" s="5">
+        <v>0</v>
+      </c>
       <c r="AH194" s="10">
         <v>2</v>
       </c>
@@ -24330,7 +25771,9 @@
       <c r="AB195" s="8">
         <v>5.6943584615384619</v>
       </c>
-      <c r="AC195" s="8"/>
+      <c r="AC195" s="8">
+        <v>10.933075000000001</v>
+      </c>
       <c r="AD195" s="8">
         <v>17.87641076923077</v>
       </c>
@@ -24459,7 +25902,9 @@
       <c r="AB196" s="8">
         <v>36.007572727272731</v>
       </c>
-      <c r="AC196" s="8"/>
+      <c r="AC196" s="8">
+        <v>54.670670000000001</v>
+      </c>
       <c r="AD196" s="8">
         <v>59.159725000000002</v>
       </c>
@@ -24510,7 +25955,7 @@
         <v>19947</v>
       </c>
       <c r="B197" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C197" s="4">
         <v>44</v>
@@ -24546,25 +25991,61 @@
       <c t="s" r="N197" s="4">
         <v>52</v>
       </c>
-      <c r="O197" s="5"/>
-      <c r="P197" s="5"/>
-      <c r="Q197" s="6"/>
-      <c r="R197" s="7"/>
-      <c r="S197" s="6"/>
-      <c r="T197" s="6"/>
-      <c r="U197" s="6"/>
-      <c r="V197" s="6"/>
-      <c r="W197" s="6"/>
-      <c r="X197" s="8"/>
-      <c r="Y197" s="6"/>
-      <c r="Z197" s="6"/>
-      <c r="AA197" s="8"/>
-      <c r="AB197" s="8"/>
-      <c r="AC197" s="8"/>
-      <c r="AD197" s="8"/>
-      <c r="AE197" s="6"/>
+      <c r="O197" s="5">
+        <v>11231.27</v>
+      </c>
+      <c r="P197" s="5">
+        <v>11231.27</v>
+      </c>
+      <c r="Q197" s="6">
+        <v>0.32845421136238118</v>
+      </c>
+      <c r="R197" s="7">
+        <v>100</v>
+      </c>
+      <c r="S197" s="6">
+        <v>0.020408163265306145</v>
+      </c>
+      <c r="T197" s="6">
+        <v>0.27902366339692664</v>
+      </c>
+      <c r="U197" s="6">
+        <v>-0.037666256799097519</v>
+      </c>
+      <c r="V197" s="6">
+        <v>0.033453741206470863</v>
+      </c>
+      <c r="W197" s="6">
+        <v>0.0099345844236671359</v>
+      </c>
+      <c r="X197" s="8">
+        <v>21.137198550724637</v>
+      </c>
+      <c r="Y197" s="6">
+        <v>0.79710144927536231</v>
+      </c>
+      <c r="Z197" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA197" s="8">
+        <v>2.1414092783505154</v>
+      </c>
+      <c r="AB197" s="8">
+        <v>5.4748797101449274</v>
+      </c>
+      <c r="AC197" s="8">
+        <v>7.7313999999999998</v>
+      </c>
+      <c r="AD197" s="8">
+        <v>14.678985507246377</v>
+      </c>
+      <c r="AE197" s="6">
+        <v>1</v>
+      </c>
       <c r="AF197" s="9"/>
-      <c r="AG197" s="5"/>
+      <c r="AG197" s="5">
+        <v>-133.53</v>
+      </c>
       <c r="AH197" s="10">
         <v>5</v>
       </c>
@@ -24683,7 +26164,9 @@
       <c r="AB198" s="8">
         <v>4.2323529411764707</v>
       </c>
-      <c r="AC198" s="8"/>
+      <c r="AC198" s="8">
+        <v>13.062744</v>
+      </c>
       <c r="AD198" s="8">
         <v>19.97941176470588</v>
       </c>
@@ -24734,7 +26217,7 @@
         <v>19951</v>
       </c>
       <c r="B199" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C199" s="4">
         <v>44</v>
@@ -24770,25 +26253,61 @@
       <c t="s" r="N199" s="4">
         <v>52</v>
       </c>
-      <c r="O199" s="5"/>
-      <c r="P199" s="5"/>
-      <c r="Q199" s="6"/>
-      <c r="R199" s="7"/>
-      <c r="S199" s="6"/>
-      <c r="T199" s="6"/>
-      <c r="U199" s="6"/>
-      <c r="V199" s="6"/>
-      <c r="W199" s="6"/>
-      <c r="X199" s="8"/>
-      <c r="Y199" s="6"/>
-      <c r="Z199" s="6"/>
-      <c r="AA199" s="8"/>
-      <c r="AB199" s="8"/>
-      <c r="AC199" s="8"/>
-      <c r="AD199" s="8"/>
-      <c r="AE199" s="6"/>
+      <c r="O199" s="5">
+        <v>6929.9200000000001</v>
+      </c>
+      <c r="P199" s="5">
+        <v>6929.9200000000001</v>
+      </c>
+      <c r="Q199" s="6">
+        <v>-0.32810483624669018</v>
+      </c>
+      <c r="R199" s="7">
+        <v>72</v>
+      </c>
+      <c r="S199" s="6">
+        <v>-0.40000000000000002</v>
+      </c>
+      <c r="T199" s="6">
+        <v>0.38803421973125229</v>
+      </c>
+      <c r="U199" s="6">
+        <v>0.039584309775581826</v>
+      </c>
+      <c r="V199" s="6">
+        <v>0.072730060375877356</v>
+      </c>
+      <c r="W199" s="6">
+        <v>0.054865496282785371</v>
+      </c>
+      <c r="X199" s="8">
+        <v>36.91282051282051</v>
+      </c>
+      <c r="Y199" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="Z199" s="6">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="AA199" s="8">
+        <v>10.467840845070421</v>
+      </c>
+      <c r="AB199" s="8">
+        <v>7.4226487179487179</v>
+      </c>
+      <c r="AC199" s="8">
+        <v>18.348717000000001</v>
+      </c>
+      <c r="AD199" s="8">
+        <v>25.295300000000001</v>
+      </c>
+      <c r="AE199" s="6">
+        <v>0.17948717948717949</v>
+      </c>
       <c r="AF199" s="9"/>
-      <c r="AG199" s="5"/>
+      <c r="AG199" s="5">
+        <v>-368.52999999999997</v>
+      </c>
       <c r="AH199" s="10">
         <v>1</v>
       </c>
@@ -24829,7 +26348,7 @@
         <v>19954</v>
       </c>
       <c r="B200" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C200" s="4">
         <v>44</v>
@@ -24865,25 +26384,61 @@
       <c t="s" r="N200" s="4">
         <v>52</v>
       </c>
-      <c r="O200" s="5"/>
-      <c r="P200" s="5"/>
-      <c r="Q200" s="6"/>
-      <c r="R200" s="7"/>
-      <c r="S200" s="6"/>
-      <c r="T200" s="6"/>
-      <c r="U200" s="6"/>
-      <c r="V200" s="6"/>
-      <c r="W200" s="6"/>
-      <c r="X200" s="8"/>
-      <c r="Y200" s="6"/>
-      <c r="Z200" s="6"/>
-      <c r="AA200" s="8"/>
-      <c r="AB200" s="8"/>
-      <c r="AC200" s="8"/>
-      <c r="AD200" s="8"/>
-      <c r="AE200" s="6"/>
+      <c r="O200" s="5">
+        <v>3767.23</v>
+      </c>
+      <c r="P200" s="5">
+        <v>3767.23</v>
+      </c>
+      <c r="Q200" s="6">
+        <v>-0.24595528849906823</v>
+      </c>
+      <c r="R200" s="7">
+        <v>46</v>
+      </c>
+      <c r="S200" s="6">
+        <v>-0.29230769230769227</v>
+      </c>
+      <c r="T200" s="6">
+        <v>0</v>
+      </c>
+      <c r="U200" s="6">
+        <v>-0.4204441990534159</v>
+      </c>
+      <c r="V200" s="6">
+        <v>0.081539752019388248</v>
+      </c>
+      <c r="W200" s="6">
+        <v>0.050944327795223551</v>
+      </c>
+      <c r="X200" s="8">
+        <v>29.719605882352941</v>
+      </c>
+      <c r="Y200" s="6">
+        <v>0.82352941176470584</v>
+      </c>
+      <c r="Z200" s="6">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="AA200" s="8">
+        <v>10.138095918367346</v>
+      </c>
+      <c r="AB200" s="8">
+        <v>4.6666647058823525</v>
+      </c>
+      <c r="AC200" s="8">
+        <v>14.936840999999999</v>
+      </c>
+      <c r="AD200" s="8">
+        <v>21.940194117647057</v>
+      </c>
+      <c r="AE200" s="6">
+        <v>0.47058823529411764</v>
+      </c>
       <c r="AF200" s="9"/>
-      <c r="AG200" s="5"/>
+      <c r="AG200" s="5">
+        <v>-100</v>
+      </c>
       <c r="AH200" s="10">
         <v>3</v>
       </c>
@@ -25095,7 +26650,9 @@
       <c r="AB202" s="8">
         <v>6.7629611111111112</v>
       </c>
-      <c r="AC202" s="8"/>
+      <c r="AC202" s="8">
+        <v>12.460330000000001</v>
+      </c>
       <c r="AD202" s="8">
         <v>18.702631578947368</v>
       </c>
@@ -25317,7 +26874,9 @@
       <c r="AB204" s="8">
         <v>5.3166653846153853</v>
       </c>
-      <c r="AC204" s="8"/>
+      <c r="AC204" s="8">
+        <v>14.570512000000001</v>
+      </c>
       <c r="AD204" s="8">
         <v>21.494230769230771</v>
       </c>
@@ -25368,7 +26927,7 @@
         <v>19959</v>
       </c>
       <c r="B205" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C205" s="4">
         <v>44</v>
@@ -25404,25 +26963,57 @@
       <c t="s" r="N205" s="4">
         <v>52</v>
       </c>
-      <c r="O205" s="5"/>
-      <c r="P205" s="5"/>
+      <c r="O205" s="5">
+        <v>4161.04</v>
+      </c>
+      <c r="P205" s="5">
+        <v>4161.04</v>
+      </c>
       <c r="Q205" s="6"/>
-      <c r="R205" s="7"/>
+      <c r="R205" s="7">
+        <v>54</v>
+      </c>
       <c r="S205" s="6"/>
-      <c r="T205" s="6"/>
-      <c r="U205" s="6"/>
-      <c r="V205" s="6"/>
-      <c r="W205" s="6"/>
-      <c r="X205" s="8"/>
-      <c r="Y205" s="6"/>
-      <c r="Z205" s="6"/>
-      <c r="AA205" s="8"/>
-      <c r="AB205" s="8"/>
-      <c r="AC205" s="8"/>
-      <c r="AD205" s="8"/>
-      <c r="AE205" s="6"/>
+      <c r="T205" s="6">
+        <v>0.29051813969584528</v>
+      </c>
+      <c r="U205" s="6">
+        <v>-0.070004710360871317</v>
+      </c>
+      <c r="V205" s="6">
+        <v>0.16539807355853342</v>
+      </c>
+      <c r="W205" s="6">
+        <v>0.11299530886509142</v>
+      </c>
+      <c r="X205" s="8">
+        <v>23.583334999999998</v>
+      </c>
+      <c r="Y205" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z205" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA205" s="8">
+        <v>4.658823529411765</v>
+      </c>
+      <c r="AB205" s="8">
+        <v>4.5791649999999997</v>
+      </c>
+      <c r="AC205" s="8">
+        <v>9.0776500000000002</v>
+      </c>
+      <c r="AD205" s="8">
+        <v>16.324165000000001</v>
+      </c>
+      <c r="AE205" s="6">
+        <v>0.90000000000000002</v>
+      </c>
       <c r="AF205" s="9"/>
-      <c r="AG205" s="5"/>
+      <c r="AG205" s="5">
+        <v>-599.79999999999995</v>
+      </c>
       <c r="AH205" s="10">
         <v>3</v>
       </c>
@@ -25463,7 +27054,7 @@
         <v>19961</v>
       </c>
       <c r="B206" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C206" s="4">
         <v>44</v>
@@ -25499,25 +27090,57 @@
       <c t="s" r="N206" s="4">
         <v>52</v>
       </c>
-      <c r="O206" s="5"/>
-      <c r="P206" s="5"/>
+      <c r="O206" s="5">
+        <v>3057.9000000000001</v>
+      </c>
+      <c r="P206" s="5">
+        <v>3057.9000000000001</v>
+      </c>
       <c r="Q206" s="6"/>
-      <c r="R206" s="7"/>
+      <c r="R206" s="7">
+        <v>38</v>
+      </c>
       <c r="S206" s="6"/>
-      <c r="T206" s="6"/>
-      <c r="U206" s="6"/>
-      <c r="V206" s="6"/>
-      <c r="W206" s="6"/>
-      <c r="X206" s="8"/>
-      <c r="Y206" s="6"/>
-      <c r="Z206" s="6"/>
-      <c r="AA206" s="8"/>
-      <c r="AB206" s="8"/>
-      <c r="AC206" s="8"/>
-      <c r="AD206" s="8"/>
-      <c r="AE206" s="6"/>
+      <c r="T206" s="6">
+        <v>0.34933238497007751</v>
+      </c>
+      <c r="U206" s="6">
+        <v>-0.0078964321920272085</v>
+      </c>
+      <c r="V206" s="6">
+        <v>0.047064161679584021</v>
+      </c>
+      <c r="W206" s="6">
+        <v>0.029957650675300044</v>
+      </c>
+      <c r="X206" s="8">
+        <v>29.223956250000001</v>
+      </c>
+      <c r="Y206" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="Z206" s="6">
+        <v>0.0625</v>
+      </c>
+      <c r="AA206" s="8">
+        <v>7.5731472222222225</v>
+      </c>
+      <c r="AB206" s="8">
+        <v>4.8104187500000002</v>
+      </c>
+      <c r="AC206" s="8">
+        <v>12.561318999999999</v>
+      </c>
+      <c r="AD206" s="8">
+        <v>19.183331249999998</v>
+      </c>
+      <c r="AE206" s="6">
+        <v>0.5</v>
+      </c>
       <c r="AF206" s="9"/>
-      <c r="AG206" s="5"/>
+      <c r="AG206" s="5">
+        <v>-403.5</v>
+      </c>
       <c r="AH206" s="10">
         <v>2</v>
       </c>
@@ -25632,7 +27255,9 @@
       <c r="AB207" s="8">
         <v>9.751148275862068</v>
       </c>
-      <c r="AC207" s="8"/>
+      <c r="AC207" s="8">
+        <v>17.428567999999999</v>
+      </c>
       <c r="AD207" s="8">
         <v>23.479570967741935</v>
       </c>
@@ -25757,7 +27382,9 @@
       <c r="AB208" s="8">
         <v>7.4683673469387752</v>
       </c>
-      <c r="AC208" s="8"/>
+      <c r="AC208" s="8">
+        <v>18.663944999999998</v>
+      </c>
       <c r="AD208" s="8">
         <v>25.607822448979594</v>
       </c>
@@ -26066,7 +27693,9 @@
       <c r="AB211" s="8">
         <v>17.895115517241379</v>
       </c>
-      <c r="AC211" s="8"/>
+      <c r="AC211" s="8">
+        <v>27.443102</v>
+      </c>
       <c r="AD211" s="8">
         <v>34.354022413793103</v>
       </c>
@@ -26541,22 +28170,24 @@
       <c t="s" r="AB216" s="14">
         <v>315</v>
       </c>
-      <c r="AC216" s="14"/>
+      <c t="s" r="AC216" s="14">
+        <v>316</v>
+      </c>
       <c t="s" r="AD216" s="14">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="AE216" s="14">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AF216" s="14"/>
       <c t="s" r="AG216" s="14">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c t="s" r="AH216" s="14">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="AI216" s="14">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AJ216" s="15"/>
       <c t="s" r="AK216" s="15">
@@ -26566,10 +28197,10 @@
         <v>52</v>
       </c>
       <c t="s" r="AM216" s="14">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="AN216" s="14">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO216" s="15"/>
       <c r="AP216" s="15"/>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-11).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-11).xlsx
@@ -911,67 +911,70 @@
     <t>GUIMARAES FRAGA,MARESSA</t>
   </si>
   <si>
-    <t>214
-162</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>R$ 1.624.530,98</t>
-  </si>
-  <si>
-    <t>R$ 9.178,14
-R$ 9.506,28</t>
-  </si>
-  <si>
-    <t>(6.6%)
+    <t>DE LOURDES RAMOS,MARIA</t>
+  </si>
+  <si>
+    <t>215
+169</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 1.679.718,18</t>
+  </si>
+  <si>
+    <t>R$ 9.128,90
+R$ 9.439,08</t>
+  </si>
+  <si>
+    <t>(6.4%)
 (3.3%)</t>
   </si>
   <si>
-    <t>98.4</t>
-  </si>
-  <si>
-    <t>(11.7%)</t>
-  </si>
-  <si>
-    <t>(8.7%)</t>
-  </si>
-  <si>
-    <t>(52.9%)</t>
+    <t>98.0</t>
+  </si>
+  <si>
+    <t>(11.3%)</t>
+  </si>
+  <si>
+    <t>(7.8%)</t>
+  </si>
+  <si>
+    <t>(51.6%)</t>
   </si>
   <si>
     <t>2.7%</t>
   </si>
   <si>
-    <t>0.7%</t>
-  </si>
-  <si>
-    <t>29.1</t>
+    <t>0.8%</t>
+  </si>
+  <si>
+    <t>29.0</t>
   </si>
   <si>
     <t>61.7%</t>
   </si>
   <si>
-    <t>14.5%</t>
-  </si>
-  <si>
-    <t>6.6</t>
-  </si>
-  <si>
-    <t>7.7</t>
+    <t>14.4%</t>
+  </si>
+  <si>
+    <t>6.5</t>
+  </si>
+  <si>
+    <t>7.6</t>
   </si>
   <si>
     <t>14.3</t>
   </si>
   <si>
-    <t>20.8</t>
-  </si>
-  <si>
-    <t>64.1%</t>
-  </si>
-  <si>
-    <t>-R$ 40.199,49</t>
+    <t>20.7</t>
+  </si>
+  <si>
+    <t>64.3%</t>
+  </si>
+  <si>
+    <t>-R$ 41.114,74</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2213,10 +2216,10 @@
         <v>-0.11851851851851847</v>
       </c>
       <c r="T7" s="6">
-        <v>0.44704859817765924</v>
+        <v>0.47814436196661553</v>
       </c>
       <c r="U7" s="6">
-        <v>-0.015826278906854098</v>
+        <v>0.015269484882102132</v>
       </c>
       <c r="V7" s="6">
         <v>0.018261867959881679</v>
@@ -3025,7 +3028,9 @@
       <c r="AB13" s="8">
         <v>5.3188555555555554</v>
       </c>
-      <c r="AC13" s="8"/>
+      <c r="AC13" s="8">
+        <v>14.234679</v>
+      </c>
       <c r="AD13" s="8">
         <v>21.188047474747474</v>
       </c>
@@ -5628,7 +5633,7 @@
         <v>19560</v>
       </c>
       <c r="B34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C34" s="4">
         <v>44</v>
@@ -5664,25 +5669,61 @@
       <c t="s" r="N34" s="4">
         <v>52</v>
       </c>
-      <c r="O34" s="5"/>
-      <c r="P34" s="5"/>
-      <c r="Q34" s="6"/>
-      <c r="R34" s="7"/>
-      <c r="S34" s="6"/>
-      <c r="T34" s="6"/>
-      <c r="U34" s="6"/>
-      <c r="V34" s="6"/>
-      <c r="W34" s="6"/>
-      <c r="X34" s="8"/>
-      <c r="Y34" s="6"/>
-      <c r="Z34" s="6"/>
-      <c r="AA34" s="8"/>
-      <c r="AB34" s="8"/>
-      <c r="AC34" s="8"/>
-      <c r="AD34" s="8"/>
-      <c r="AE34" s="6"/>
+      <c r="O34" s="5">
+        <v>13297.469999999999</v>
+      </c>
+      <c r="P34" s="5">
+        <v>13297.469999999999</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>-0.052685009129437188</v>
+      </c>
+      <c r="R34" s="7">
+        <v>177</v>
+      </c>
+      <c r="S34" s="6">
+        <v>0.14193548387096766</v>
+      </c>
+      <c r="T34" s="6">
+        <v>0.028092561968554922</v>
+      </c>
+      <c r="U34" s="6">
+        <v>-0.30317797295274967</v>
+      </c>
+      <c r="V34" s="6">
+        <v>0.04472038666001879</v>
+      </c>
+      <c r="W34" s="6">
+        <v>0.023474239836600498</v>
+      </c>
+      <c r="X34" s="8">
+        <v>19.382086394557824</v>
+      </c>
+      <c r="Y34" s="6">
+        <v>0.6462585034013606</v>
+      </c>
+      <c r="Z34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="8">
+        <v>6.816193181818182</v>
+      </c>
+      <c r="AB34" s="8">
+        <v>2.1063220689655173</v>
+      </c>
+      <c r="AC34" s="8">
+        <v>9.4201720000000009</v>
+      </c>
+      <c r="AD34" s="8">
+        <v>15.317573469387757</v>
+      </c>
+      <c r="AE34" s="6">
+        <v>0.95238095238095233</v>
+      </c>
       <c r="AF34" s="9"/>
-      <c r="AG34" s="5"/>
+      <c r="AG34" s="5">
+        <v>-55.899999999999999</v>
+      </c>
       <c r="AH34" s="10">
         <v>4</v>
       </c>
@@ -5777,10 +5818,10 @@
         <v>0.30769230769230771</v>
       </c>
       <c r="T35" s="6">
-        <v>0.32508926667367505</v>
+        <v>0.32313393004640545</v>
       </c>
       <c r="U35" s="6">
-        <v>0.0003201676002823374</v>
+        <v>-0.0016351690269872498</v>
       </c>
       <c r="V35" s="6">
         <v>0.060255154910117591</v>
@@ -5858,7 +5899,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5894,25 +5935,61 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="O36" s="5">
+        <v>5620.4799999999996</v>
+      </c>
+      <c r="P36" s="5">
+        <v>5620.4799999999996</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0.15672965708570175</v>
+      </c>
+      <c r="R36" s="7">
+        <v>68</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.23636363636363633</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.3232553981154635</v>
+      </c>
+      <c r="U36" s="6">
+        <v>0.012426073929628788</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.072126757856980195</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.033445008255522664</v>
+      </c>
+      <c r="X36" s="8">
+        <v>25.105847368421053</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>0.92982456140350878</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>5.0260869565217394</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>4.6786543859649115</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>9.6856709999999993</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>16.640057894736842</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.78947368421052633</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -6608,7 +6685,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6644,25 +6721,61 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
-      <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="O42" s="5">
+        <v>5819.6700000000001</v>
+      </c>
+      <c r="P42" s="5">
+        <v>5819.6700000000001</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>-0.37955683773531801</v>
+      </c>
+      <c r="R42" s="7">
+        <v>52</v>
+      </c>
+      <c r="S42" s="6">
+        <v>-0.45263157894736838</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.37733209958640268</v>
+      </c>
+      <c r="U42" s="6">
+        <v>0.072453987940896997</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.023754697431297649</v>
+      </c>
+      <c r="W42" s="6">
+        <v>-0.0025663826299429349</v>
+      </c>
+      <c r="X42" s="8">
+        <v>32.344608823529413</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0.088235294117647065</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>5.2871788461538456</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>8.5205882352941167</v>
+      </c>
+      <c r="AC42" s="8">
+        <v>14.194117</v>
+      </c>
+      <c r="AD42" s="8">
+        <v>21.148529411764706</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.61764705882352944</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -10846,7 +10959,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>44</v>
@@ -10880,25 +10993,61 @@
       <c t="s" r="N76" s="4">
         <v>52</v>
       </c>
-      <c r="O76" s="5"/>
-      <c r="P76" s="5"/>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="7"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
-      <c r="V76" s="6"/>
-      <c r="W76" s="6"/>
-      <c r="X76" s="8"/>
-      <c r="Y76" s="6"/>
-      <c r="Z76" s="6"/>
-      <c r="AA76" s="8"/>
-      <c r="AB76" s="8"/>
-      <c r="AC76" s="8"/>
-      <c r="AD76" s="8"/>
-      <c r="AE76" s="6"/>
+      <c r="O76" s="5">
+        <v>10914.24</v>
+      </c>
+      <c r="P76" s="5">
+        <v>10914.24</v>
+      </c>
+      <c r="Q76" s="6">
+        <v>0.12137595166908111</v>
+      </c>
+      <c r="R76" s="7">
+        <v>130</v>
+      </c>
+      <c r="S76" s="6">
+        <v>0.065573770491803351</v>
+      </c>
+      <c r="T76" s="6">
+        <v>-0.066831378089541732</v>
+      </c>
+      <c r="U76" s="6">
+        <v>-0.4288025277069224</v>
+      </c>
+      <c r="V76" s="6">
+        <v>0.022465558756267042</v>
+      </c>
+      <c r="W76" s="6">
+        <v>0.0077874868062274612</v>
+      </c>
+      <c r="X76" s="8">
+        <v>32.882035064935067</v>
+      </c>
+      <c r="Y76" s="6">
+        <v>0.23376623376623376</v>
+      </c>
+      <c r="Z76" s="6">
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="AA76" s="8">
+        <v>4.5643592307692309</v>
+      </c>
+      <c r="AB76" s="8">
+        <v>8.89054054054054</v>
+      </c>
+      <c r="AC76" s="8">
+        <v>13.338403</v>
+      </c>
+      <c r="AD76" s="8">
+        <v>21.86017272727273</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>0.4935064935064935</v>
+      </c>
       <c r="AF76" s="9"/>
-      <c r="AG76" s="5"/>
+      <c r="AG76" s="5">
+        <v>-152.5</v>
+      </c>
       <c r="AH76" s="10">
         <v>2</v>
       </c>
@@ -15844,7 +15993,9 @@
       <c r="Z116" s="6"/>
       <c r="AA116" s="8"/>
       <c r="AB116" s="8"/>
-      <c r="AC116" s="8"/>
+      <c r="AC116" s="8">
+        <v>30.782063000000001</v>
+      </c>
       <c r="AD116" s="8"/>
       <c r="AE116" s="6"/>
       <c r="AF116" s="9"/>
@@ -18364,7 +18515,7 @@
         <v>19785</v>
       </c>
       <c r="B136" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C136" s="4">
         <v>44</v>
@@ -18400,25 +18551,61 @@
       <c t="s" r="N136" s="4">
         <v>52</v>
       </c>
-      <c r="O136" s="5"/>
-      <c r="P136" s="5"/>
-      <c r="Q136" s="6"/>
-      <c r="R136" s="7"/>
-      <c r="S136" s="6"/>
-      <c r="T136" s="6"/>
-      <c r="U136" s="6"/>
-      <c r="V136" s="6"/>
-      <c r="W136" s="6"/>
-      <c r="X136" s="8"/>
-      <c r="Y136" s="6"/>
-      <c r="Z136" s="6"/>
-      <c r="AA136" s="8"/>
-      <c r="AB136" s="8"/>
-      <c r="AC136" s="8"/>
-      <c r="AD136" s="8"/>
-      <c r="AE136" s="6"/>
+      <c r="O136" s="5">
+        <v>11214.24</v>
+      </c>
+      <c r="P136" s="5">
+        <v>11214.24</v>
+      </c>
+      <c r="Q136" s="6">
+        <v>0.0011534354879603193</v>
+      </c>
+      <c r="R136" s="7">
+        <v>97</v>
+      </c>
+      <c r="S136" s="6">
+        <v>-0.030000000000000027</v>
+      </c>
+      <c r="T136" s="6">
+        <v>0.26487976893663767</v>
+      </c>
+      <c r="U136" s="6">
+        <v>-0.0044599277347372622</v>
+      </c>
+      <c r="V136" s="6">
+        <v>0.009512102469717074</v>
+      </c>
+      <c r="W136" s="6">
+        <v>-0.001682592846238354</v>
+      </c>
+      <c r="X136" s="8">
+        <v>43.415124074074079</v>
+      </c>
+      <c r="Y136" s="6">
+        <v>0.20370370370370369</v>
+      </c>
+      <c r="Z136" s="6">
+        <v>0.51851851851851849</v>
+      </c>
+      <c r="AA136" s="8">
+        <v>6.8192443298969065</v>
+      </c>
+      <c r="AB136" s="8">
+        <v>21.10709814814815</v>
+      </c>
+      <c r="AC136" s="8">
+        <v>27.831789000000001</v>
+      </c>
+      <c r="AD136" s="8">
+        <v>34.597222222222221</v>
+      </c>
+      <c r="AE136" s="6">
+        <v>0.25925925925925924</v>
+      </c>
       <c r="AF136" s="9"/>
-      <c r="AG136" s="5"/>
+      <c r="AG136" s="5">
+        <v>-472.89999999999998</v>
+      </c>
       <c r="AH136" s="10">
         <v>2</v>
       </c>
@@ -18941,7 +19128,7 @@
         <v>19793</v>
       </c>
       <c r="B141" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C141" s="4">
         <v>44</v>
@@ -18977,25 +19164,61 @@
       <c t="s" r="N141" s="4">
         <v>52</v>
       </c>
-      <c r="O141" s="5"/>
-      <c r="P141" s="5"/>
-      <c r="Q141" s="6"/>
-      <c r="R141" s="7"/>
-      <c r="S141" s="6"/>
-      <c r="T141" s="6"/>
-      <c r="U141" s="6"/>
-      <c r="V141" s="6"/>
-      <c r="W141" s="6"/>
-      <c r="X141" s="8"/>
-      <c r="Y141" s="6"/>
-      <c r="Z141" s="6"/>
-      <c r="AA141" s="8"/>
-      <c r="AB141" s="8"/>
-      <c r="AC141" s="8"/>
-      <c r="AD141" s="8"/>
-      <c r="AE141" s="6"/>
+      <c r="O141" s="5">
+        <v>5529.8999999999996</v>
+      </c>
+      <c r="P141" s="5">
+        <v>5529.8999999999996</v>
+      </c>
+      <c r="Q141" s="6">
+        <v>0.095532997337390402</v>
+      </c>
+      <c r="R141" s="7">
+        <v>60</v>
+      </c>
+      <c r="S141" s="6">
+        <v>0.090909090909090828</v>
+      </c>
+      <c r="T141" s="6">
+        <v>0.36385413841118286</v>
+      </c>
+      <c r="U141" s="6">
+        <v>0.055423606213493924</v>
+      </c>
+      <c r="V141" s="6">
+        <v>0.080973616159424222</v>
+      </c>
+      <c r="W141" s="6">
+        <v>0.037032496066836652</v>
+      </c>
+      <c r="X141" s="8">
+        <v>22.528124999999999</v>
+      </c>
+      <c r="Y141" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z141" s="6">
+        <v>0.03125</v>
+      </c>
+      <c r="AA141" s="8">
+        <v>3.2758620689655173</v>
+      </c>
+      <c r="AB141" s="8">
+        <v>4.5250000000000004</v>
+      </c>
+      <c r="AC141" s="8">
+        <v>7.7854159999999997</v>
+      </c>
+      <c r="AD141" s="8">
+        <v>15.737500000000001</v>
+      </c>
+      <c r="AE141" s="6">
+        <v>0.78125</v>
+      </c>
       <c r="AF141" s="9"/>
-      <c r="AG141" s="5"/>
+      <c r="AG141" s="5">
+        <v>0</v>
+      </c>
       <c r="AH141" s="10">
         <v>4</v>
       </c>
@@ -24685,7 +24908,7 @@
         <v>19927</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C187" s="4">
         <v>44</v>
@@ -24721,25 +24944,61 @@
       <c t="s" r="N187" s="4">
         <v>52</v>
       </c>
-      <c r="O187" s="5"/>
-      <c r="P187" s="5"/>
-      <c r="Q187" s="6"/>
-      <c r="R187" s="7"/>
-      <c r="S187" s="6"/>
-      <c r="T187" s="6"/>
-      <c r="U187" s="6"/>
-      <c r="V187" s="6"/>
-      <c r="W187" s="6"/>
-      <c r="X187" s="8"/>
-      <c r="Y187" s="6"/>
-      <c r="Z187" s="6"/>
-      <c r="AA187" s="8"/>
-      <c r="AB187" s="8"/>
-      <c r="AC187" s="8"/>
-      <c r="AD187" s="8"/>
-      <c r="AE187" s="6"/>
+      <c r="O187" s="5">
+        <v>2791.1999999999998</v>
+      </c>
+      <c r="P187" s="5">
+        <v>2791.1999999999998</v>
+      </c>
+      <c r="Q187" s="6">
+        <v>0.06378032280808732</v>
+      </c>
+      <c r="R187" s="7">
+        <v>33</v>
+      </c>
+      <c r="S187" s="6">
+        <v>-0.10810810810810811</v>
+      </c>
+      <c r="T187" s="6">
+        <v>0</v>
+      </c>
+      <c r="U187" s="6">
+        <v>-0.29833046718257383</v>
+      </c>
+      <c r="V187" s="6">
+        <v>0.24039660361134998</v>
+      </c>
+      <c r="W187" s="6">
+        <v>0.204920822585268</v>
+      </c>
+      <c r="X187" s="8">
+        <v>31.652779166666665</v>
+      </c>
+      <c r="Y187" s="6">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="Z187" s="6">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="AA187" s="8">
+        <v>8.7409090909090903</v>
+      </c>
+      <c r="AB187" s="8">
+        <v>8.4608695652173918</v>
+      </c>
+      <c r="AC187" s="8">
+        <v>16.860869000000001</v>
+      </c>
+      <c r="AD187" s="8">
+        <v>23.357637499999999</v>
+      </c>
+      <c r="AE187" s="6">
+        <v>0.41666666666666669</v>
+      </c>
       <c r="AF187" s="9"/>
-      <c r="AG187" s="5"/>
+      <c r="AG187" s="5">
+        <v>-233.94999999999999</v>
+      </c>
       <c r="AH187" s="10">
         <v>1</v>
       </c>
@@ -28107,112 +28366,203 @@
         <v>56</v>
       </c>
     </row>
-    <row r="216" ht="24.75" customHeight="1">
-      <c t="s" r="A216" s="14">
+    <row r="216" ht="13.5" customHeight="1">
+      <c r="A216" s="2">
+        <v>19980</v>
+      </c>
+      <c r="B216" s="3">
+        <v>-1</v>
+      </c>
+      <c t="s" r="C216" s="4">
+        <v>44</v>
+      </c>
+      <c t="s" r="D216" s="4">
+        <v>45</v>
+      </c>
+      <c t="s" r="E216" s="4">
+        <v>46</v>
+      </c>
+      <c t="s" r="F216" s="4">
+        <v>47</v>
+      </c>
+      <c t="s" r="G216" s="4">
+        <v>48</v>
+      </c>
+      <c t="s" r="H216" s="4">
+        <v>49</v>
+      </c>
+      <c t="s" r="I216" s="4">
+        <v>50</v>
+      </c>
+      <c t="s" r="J216" s="4">
+        <v>47</v>
+      </c>
+      <c t="s" r="K216" s="4">
+        <v>51</v>
+      </c>
+      <c t="s" r="L216" s="4">
+        <v>51</v>
+      </c>
+      <c r="M216" s="4"/>
+      <c t="s" r="N216" s="4">
+        <v>52</v>
+      </c>
+      <c r="O216" s="5"/>
+      <c r="P216" s="5"/>
+      <c r="Q216" s="6"/>
+      <c r="R216" s="7"/>
+      <c r="S216" s="6"/>
+      <c r="T216" s="6"/>
+      <c r="U216" s="6"/>
+      <c r="V216" s="6"/>
+      <c r="W216" s="6"/>
+      <c r="X216" s="8"/>
+      <c r="Y216" s="6"/>
+      <c r="Z216" s="6"/>
+      <c r="AA216" s="8"/>
+      <c r="AB216" s="8"/>
+      <c r="AC216" s="8"/>
+      <c r="AD216" s="8"/>
+      <c r="AE216" s="6"/>
+      <c r="AF216" s="9"/>
+      <c r="AG216" s="5"/>
+      <c r="AH216" s="10"/>
+      <c r="AI216" s="11"/>
+      <c r="AJ216" s="12"/>
+      <c t="s" r="AK216" s="4">
+        <v>52</v>
+      </c>
+      <c t="s" r="AL216" s="4">
+        <v>52</v>
+      </c>
+      <c r="AM216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AN216" s="2">
+        <v>1</v>
+      </c>
+      <c t="s" r="AO216" s="4">
+        <v>53</v>
+      </c>
+      <c t="s" r="AP216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="AQ216" s="4">
+        <v>55</v>
+      </c>
+      <c t="s" r="AR216" s="4">
         <v>300</v>
       </c>
-      <c t="s" r="B216" s="14">
+      <c t="s" r="AS216" s="4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="217" ht="24.75" customHeight="1">
+      <c t="s" r="A217" s="14">
         <v>301</v>
       </c>
-      <c r="C216" s="15"/>
-      <c r="D216" s="15"/>
-      <c r="E216" s="15"/>
-      <c r="F216" s="15"/>
-      <c r="G216" s="15"/>
-      <c r="H216" s="15"/>
-      <c r="I216" s="15"/>
-      <c r="J216" s="15"/>
-      <c r="K216" s="15"/>
-      <c r="L216" s="15"/>
-      <c r="M216" s="15"/>
-      <c t="s" r="N216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="O216" s="14">
+      <c t="s" r="B217" s="14">
         <v>302</v>
       </c>
-      <c t="s" r="P216" s="14">
+      <c r="C217" s="15"/>
+      <c r="D217" s="15"/>
+      <c r="E217" s="15"/>
+      <c r="F217" s="15"/>
+      <c r="G217" s="15"/>
+      <c r="H217" s="15"/>
+      <c r="I217" s="15"/>
+      <c r="J217" s="15"/>
+      <c r="K217" s="15"/>
+      <c r="L217" s="15"/>
+      <c r="M217" s="15"/>
+      <c t="s" r="N217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="O217" s="14">
         <v>303</v>
       </c>
-      <c t="s" r="Q216" s="14">
+      <c t="s" r="P217" s="14">
         <v>304</v>
       </c>
-      <c t="s" r="R216" s="14">
+      <c t="s" r="Q217" s="14">
         <v>305</v>
       </c>
-      <c t="s" r="S216" s="14">
+      <c t="s" r="R217" s="14">
         <v>306</v>
       </c>
-      <c t="s" r="T216" s="14">
+      <c t="s" r="S217" s="14">
         <v>307</v>
       </c>
-      <c t="s" r="U216" s="14">
+      <c t="s" r="T217" s="14">
         <v>308</v>
       </c>
-      <c t="s" r="V216" s="14">
+      <c t="s" r="U217" s="14">
         <v>309</v>
       </c>
-      <c t="s" r="W216" s="14">
+      <c t="s" r="V217" s="14">
         <v>310</v>
       </c>
-      <c t="s" r="X216" s="14">
+      <c t="s" r="W217" s="14">
         <v>311</v>
       </c>
-      <c t="s" r="Y216" s="14">
+      <c t="s" r="X217" s="14">
         <v>312</v>
       </c>
-      <c t="s" r="Z216" s="14">
+      <c t="s" r="Y217" s="14">
         <v>313</v>
       </c>
-      <c t="s" r="AA216" s="14">
+      <c t="s" r="Z217" s="14">
         <v>314</v>
       </c>
-      <c t="s" r="AB216" s="14">
+      <c t="s" r="AA217" s="14">
         <v>315</v>
       </c>
-      <c t="s" r="AC216" s="14">
+      <c t="s" r="AB217" s="14">
         <v>316</v>
       </c>
-      <c t="s" r="AD216" s="14">
+      <c t="s" r="AC217" s="14">
         <v>317</v>
       </c>
-      <c t="s" r="AE216" s="14">
+      <c t="s" r="AD217" s="14">
         <v>318</v>
       </c>
-      <c r="AF216" s="14"/>
-      <c t="s" r="AG216" s="14">
+      <c t="s" r="AE217" s="14">
         <v>319</v>
       </c>
-      <c t="s" r="AH216" s="14">
+      <c r="AF217" s="14"/>
+      <c t="s" r="AG217" s="14">
         <v>320</v>
       </c>
-      <c t="s" r="AI216" s="14">
+      <c t="s" r="AH217" s="14">
         <v>321</v>
       </c>
-      <c r="AJ216" s="15"/>
-      <c t="s" r="AK216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="AL216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="AM216" s="14">
+      <c t="s" r="AI217" s="14">
         <v>322</v>
       </c>
-      <c t="s" r="AN216" s="14">
-        <v>322</v>
-      </c>
-      <c r="AO216" s="15"/>
-      <c r="AP216" s="15"/>
-      <c r="AQ216" s="15"/>
-      <c r="AR216" s="15"/>
-      <c r="AS216" s="15"/>
+      <c r="AJ217" s="15"/>
+      <c t="s" r="AK217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="AL217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="AM217" s="14">
+        <v>323</v>
+      </c>
+      <c t="s" r="AN217" s="14">
+        <v>323</v>
+      </c>
+      <c r="AO217" s="15"/>
+      <c r="AP217" s="15"/>
+      <c r="AQ217" s="15"/>
+      <c r="AR217" s="15"/>
+      <c r="AS217" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AS216" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:AS217" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-11).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-11).xlsx
@@ -915,33 +915,33 @@
   </si>
   <si>
     <t>215
-169</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>R$ 1.679.718,18</t>
-  </si>
-  <si>
-    <t>R$ 9.128,90
-R$ 9.439,08</t>
-  </si>
-  <si>
-    <t>(6.4%)
-(3.3%)</t>
-  </si>
-  <si>
-    <t>98.0</t>
-  </si>
-  <si>
-    <t>(11.3%)</t>
-  </si>
-  <si>
-    <t>(7.8%)</t>
-  </si>
-  <si>
-    <t>(51.6%)</t>
+170</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 1.692.580,78</t>
+  </si>
+  <si>
+    <t>R$ 9.149,09
+R$ 9.459,22</t>
+  </si>
+  <si>
+    <t>(6.2%)
+(3.0%)</t>
+  </si>
+  <si>
+    <t>98.2</t>
+  </si>
+  <si>
+    <t>(11.1%)</t>
+  </si>
+  <si>
+    <t>(7.6%)</t>
+  </si>
+  <si>
+    <t>(51.2%)</t>
   </si>
   <si>
     <t>2.7%</t>
@@ -950,28 +950,28 @@
     <t>0.8%</t>
   </si>
   <si>
-    <t>29.0</t>
-  </si>
-  <si>
-    <t>61.7%</t>
-  </si>
-  <si>
-    <t>14.4%</t>
+    <t>29.2</t>
+  </si>
+  <si>
+    <t>61.3%</t>
+  </si>
+  <si>
+    <t>15.0%</t>
   </si>
   <si>
     <t>6.5</t>
   </si>
   <si>
-    <t>7.6</t>
+    <t>7.8</t>
   </si>
   <si>
     <t>14.3</t>
   </si>
   <si>
-    <t>20.7</t>
-  </si>
-  <si>
-    <t>64.3%</t>
+    <t>20.9</t>
+  </si>
+  <si>
+    <t>63.9%</t>
   </si>
   <si>
     <t>-R$ 41.114,74</t>
@@ -11049,7 +11049,7 @@
         <v>-152.5</v>
       </c>
       <c r="AH76" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI76" s="11"/>
       <c r="AJ76" s="13">
@@ -16523,7 +16523,7 @@
         <v>0</v>
       </c>
       <c r="AH120" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI120" s="11"/>
       <c r="AJ120" s="13">
@@ -21378,7 +21378,7 @@
         <v>19863</v>
       </c>
       <c r="B159" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C159" s="4">
         <v>44</v>
@@ -21414,27 +21414,61 @@
       <c t="s" r="N159" s="4">
         <v>52</v>
       </c>
-      <c r="O159" s="5"/>
-      <c r="P159" s="5"/>
-      <c r="Q159" s="6"/>
-      <c r="R159" s="7"/>
-      <c r="S159" s="6"/>
-      <c r="T159" s="6"/>
-      <c r="U159" s="6"/>
-      <c r="V159" s="6"/>
-      <c r="W159" s="6"/>
-      <c r="X159" s="8"/>
-      <c r="Y159" s="6"/>
-      <c r="Z159" s="6"/>
-      <c r="AA159" s="8"/>
-      <c r="AB159" s="8"/>
+      <c r="O159" s="5">
+        <v>12862.6</v>
+      </c>
+      <c r="P159" s="5">
+        <v>12862.6</v>
+      </c>
+      <c r="Q159" s="6">
+        <v>0.45525431821087436</v>
+      </c>
+      <c r="R159" s="7">
+        <v>123</v>
+      </c>
+      <c r="S159" s="6">
+        <v>0.3085106382978724</v>
+      </c>
+      <c r="T159" s="6">
+        <v>0.27450610296518591</v>
+      </c>
+      <c r="U159" s="6">
+        <v>-0.019341175190085987</v>
+      </c>
+      <c r="V159" s="6">
+        <v>0.020609557943184111</v>
+      </c>
+      <c r="W159" s="6">
+        <v>0.0012658793712002237</v>
+      </c>
+      <c r="X159" s="8">
+        <v>51.822875490196076</v>
+      </c>
+      <c r="Y159" s="6">
+        <v>0.14705882352941177</v>
+      </c>
+      <c r="Z159" s="6">
+        <v>0.80392156862745101</v>
+      </c>
+      <c r="AA159" s="8">
+        <v>6.3981336000000004</v>
+      </c>
+      <c r="AB159" s="8">
+        <v>20.829738235294116</v>
+      </c>
       <c r="AC159" s="8">
         <v>27.563872</v>
       </c>
-      <c r="AD159" s="8"/>
-      <c r="AE159" s="6"/>
+      <c r="AD159" s="8">
+        <v>34.432352941176468</v>
+      </c>
+      <c r="AE159" s="6">
+        <v>0.12745098039215685</v>
+      </c>
       <c r="AF159" s="9"/>
-      <c r="AG159" s="5"/>
+      <c r="AG159" s="5">
+        <v>0</v>
+      </c>
       <c r="AH159" s="10">
         <v>2</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-11).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-11).xlsx
@@ -915,33 +915,33 @@
   </si>
   <si>
     <t>215
-170</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 1.692.580,78</t>
-  </si>
-  <si>
-    <t>R$ 9.149,09
-R$ 9.459,22</t>
-  </si>
-  <si>
-    <t>(6.2%)
-(3.0%)</t>
+171</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 1.702.823,87</t>
+  </si>
+  <si>
+    <t>R$ 9.154,97
+R$ 9.463,81</t>
+  </si>
+  <si>
+    <t>(6.3%)
+(3.2%)</t>
   </si>
   <si>
     <t>98.2</t>
   </si>
   <si>
-    <t>(11.1%)</t>
-  </si>
-  <si>
-    <t>(7.6%)</t>
-  </si>
-  <si>
-    <t>(51.2%)</t>
+    <t>(11.3%)</t>
+  </si>
+  <si>
+    <t>(7.5%)</t>
+  </si>
+  <si>
+    <t>(51.1%)</t>
   </si>
   <si>
     <t>2.7%</t>
@@ -950,7 +950,7 @@
     <t>0.8%</t>
   </si>
   <si>
-    <t>29.2</t>
+    <t>29.3</t>
   </si>
   <si>
     <t>61.3%</t>
@@ -971,7 +971,7 @@
     <t>20.9</t>
   </si>
   <si>
-    <t>63.9%</t>
+    <t>63.7%</t>
   </si>
   <si>
     <t>-R$ 41.114,74</t>
@@ -4812,7 +4812,7 @@
         <v>-993.5</v>
       </c>
       <c r="AH27" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI27" s="11"/>
       <c r="AJ27" s="13">
@@ -12610,7 +12610,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12644,25 +12644,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>10243.09</v>
+      </c>
+      <c r="P89" s="5">
+        <v>10243.09</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.22931670644319579</v>
+      </c>
+      <c r="R89" s="7">
+        <v>93</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.31111111111111112</v>
+      </c>
+      <c r="T89" s="6">
+        <v>0.00024689815280349973</v>
+      </c>
+      <c r="U89" s="6">
+        <v>-0.31204265509724116</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.019742235985430175</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.0069345773589805414</v>
+      </c>
+      <c r="X89" s="8">
+        <v>32.40625</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>0.6071428571428571</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.16071428571428573</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>7.1789010638297865</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>8.5684854545454545</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>23.631844642857143</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.4107142857142857</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>0</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -14192,7 +14226,7 @@
         <v>0</v>
       </c>
       <c r="AH101" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI101" s="11"/>
       <c r="AJ101" s="13">
@@ -24718,7 +24752,7 @@
         <v>19923</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>44</v>
@@ -25685,7 +25719,7 @@
         <v>0</v>
       </c>
       <c r="AH192" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI192" s="11"/>
       <c r="AJ192" s="13">
@@ -26996,7 +27030,7 @@
         <v>19957</v>
       </c>
       <c r="B203" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C203" s="4">
         <v>44</v>
@@ -28405,7 +28439,7 @@
         <v>19980</v>
       </c>
       <c r="B216" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c t="s" r="C216" s="4">
         <v>44</v>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-11).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-11).xlsx
@@ -915,33 +915,33 @@
   </si>
   <si>
     <t>215
-171</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 1.702.823,87</t>
-  </si>
-  <si>
-    <t>R$ 9.154,97
-R$ 9.463,81</t>
-  </si>
-  <si>
-    <t>(6.3%)
-(3.2%)</t>
-  </si>
-  <si>
-    <t>98.2</t>
-  </si>
-  <si>
-    <t>(11.3%)</t>
-  </si>
-  <si>
-    <t>(7.5%)</t>
-  </si>
-  <si>
-    <t>(51.1%)</t>
+177</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>R$ 1.752.480,12</t>
+  </si>
+  <si>
+    <t>R$ 9.127,50
+R$ 9.423,54</t>
+  </si>
+  <si>
+    <t>(5.7%)
+(2.6%)</t>
+  </si>
+  <si>
+    <t>97.6</t>
+  </si>
+  <si>
+    <t>(10.8%)</t>
+  </si>
+  <si>
+    <t>(6.6%)</t>
+  </si>
+  <si>
+    <t>(49.7%)</t>
   </si>
   <si>
     <t>2.7%</t>
@@ -950,31 +950,31 @@
     <t>0.8%</t>
   </si>
   <si>
-    <t>29.3</t>
-  </si>
-  <si>
-    <t>61.3%</t>
-  </si>
-  <si>
-    <t>15.0%</t>
-  </si>
-  <si>
-    <t>6.5</t>
+    <t>29.7</t>
+  </si>
+  <si>
+    <t>60.8%</t>
+  </si>
+  <si>
+    <t>15.7%</t>
+  </si>
+  <si>
+    <t>6.7</t>
   </si>
   <si>
     <t>7.8</t>
   </si>
   <si>
-    <t>14.3</t>
-  </si>
-  <si>
-    <t>20.9</t>
-  </si>
-  <si>
-    <t>63.7%</t>
-  </si>
-  <si>
-    <t>-R$ 41.114,74</t>
+    <t>14.6</t>
+  </si>
+  <si>
+    <t>21.2</t>
+  </si>
+  <si>
+    <t>63.1%</t>
+  </si>
+  <si>
+    <t>-R$ 40.962,74</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2069,7 +2069,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2105,25 +2105,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>14034.59</v>
+      </c>
+      <c r="P6" s="5">
+        <v>14034.59</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0.18230923912997699</v>
+      </c>
+      <c r="R6" s="7">
+        <v>130</v>
+      </c>
+      <c r="S6" s="6">
+        <v>0.015625</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.26636079144456659</v>
+      </c>
+      <c r="U6" s="6">
+        <v>-0.0015194957601183934</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.022332800601941344</v>
+      </c>
+      <c r="W6" s="6">
+        <v>0.00029368153968160096</v>
+      </c>
+      <c r="X6" s="8">
+        <v>22.102040816326532</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0.01020408163265306</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>6.2226100775193798</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>2.5454081632653058</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>8.6433669999999996</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>15.603741836734693</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0.89795918367346939</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>0</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -7858,7 +7894,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7894,25 +7930,59 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
+      <c r="O51" s="5">
+        <v>1115.02</v>
+      </c>
+      <c r="P51" s="5">
+        <v>1115.02</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.43163131629787077</v>
+      </c>
+      <c r="R51" s="7">
+        <v>10</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.47368421052631582</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.3488188552671701</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.018432853222363727</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.096372262380943832</v>
+      </c>
+      <c r="X51" s="8">
+        <v>38.938100000000006</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>6.4249999999999998</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>19.216671428571427</v>
+      </c>
       <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="AD51" s="8">
+        <v>32.111899999999999</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0.42857142857142855</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -8785,7 +8855,9 @@
       <c r="Z58" s="6"/>
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="8">
+        <v>12.628219</v>
+      </c>
       <c r="AD58" s="8"/>
       <c r="AE58" s="6"/>
       <c r="AF58" s="9"/>
@@ -20472,7 +20544,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>44</v>
@@ -20508,25 +20580,61 @@
       <c t="s" r="N151" s="4">
         <v>52</v>
       </c>
-      <c r="O151" s="5"/>
-      <c r="P151" s="5"/>
-      <c r="Q151" s="6"/>
-      <c r="R151" s="7"/>
-      <c r="S151" s="6"/>
-      <c r="T151" s="6"/>
-      <c r="U151" s="6"/>
-      <c r="V151" s="6"/>
-      <c r="W151" s="6"/>
-      <c r="X151" s="8"/>
-      <c r="Y151" s="6"/>
-      <c r="Z151" s="6"/>
-      <c r="AA151" s="8"/>
-      <c r="AB151" s="8"/>
-      <c r="AC151" s="8"/>
-      <c r="AD151" s="8"/>
-      <c r="AE151" s="6"/>
+      <c r="O151" s="5">
+        <v>8479.4899999999998</v>
+      </c>
+      <c r="P151" s="5">
+        <v>8479.4899999999998</v>
+      </c>
+      <c r="Q151" s="6">
+        <v>0.14501207871351229</v>
+      </c>
+      <c r="R151" s="7">
+        <v>100</v>
+      </c>
+      <c r="S151" s="6">
+        <v>0.21951219512195119</v>
+      </c>
+      <c r="T151" s="6">
+        <v>0.28277356303268242</v>
+      </c>
+      <c r="U151" s="6">
+        <v>-0.023687084954401739</v>
+      </c>
+      <c r="V151" s="6">
+        <v>0.029628963534363506</v>
+      </c>
+      <c r="W151" s="6">
+        <v>0.0099119758381695129</v>
+      </c>
+      <c r="X151" s="8">
+        <v>67.37222222222222</v>
+      </c>
+      <c r="Y151" s="6">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="Z151" s="6">
+        <v>0.81111111111111112</v>
+      </c>
+      <c r="AA151" s="8">
+        <v>29.624411111111108</v>
+      </c>
+      <c r="AB151" s="8">
+        <v>14.817407777777779</v>
+      </c>
+      <c r="AC151" s="8">
+        <v>45.630184</v>
+      </c>
+      <c r="AD151" s="8">
+        <v>52.559258888888891</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>0.12222222222222222</v>
+      </c>
       <c r="AF151" s="9"/>
-      <c r="AG151" s="5"/>
+      <c r="AG151" s="5">
+        <v>0</v>
+      </c>
       <c r="AH151" s="10">
         <v>5</v>
       </c>
@@ -21222,7 +21330,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>44</v>
@@ -21258,25 +21366,61 @@
       <c t="s" r="N157" s="4">
         <v>52</v>
       </c>
-      <c r="O157" s="5"/>
-      <c r="P157" s="5"/>
-      <c r="Q157" s="6"/>
-      <c r="R157" s="7"/>
-      <c r="S157" s="6"/>
-      <c r="T157" s="6"/>
-      <c r="U157" s="6"/>
-      <c r="V157" s="6"/>
-      <c r="W157" s="6"/>
-      <c r="X157" s="8"/>
-      <c r="Y157" s="6"/>
-      <c r="Z157" s="6"/>
-      <c r="AA157" s="8"/>
-      <c r="AB157" s="8"/>
-      <c r="AC157" s="8"/>
-      <c r="AD157" s="8"/>
-      <c r="AE157" s="6"/>
+      <c r="O157" s="5">
+        <v>5478.0799999999999</v>
+      </c>
+      <c r="P157" s="5">
+        <v>5478.0799999999999</v>
+      </c>
+      <c r="Q157" s="6">
+        <v>-0.15173343945543261</v>
+      </c>
+      <c r="R157" s="7">
+        <v>63</v>
+      </c>
+      <c r="S157" s="6">
+        <v>-0.099999999999999978</v>
+      </c>
+      <c r="T157" s="6">
+        <v>0.29641730314270698</v>
+      </c>
+      <c r="U157" s="6">
+        <v>0.011697109206145218</v>
+      </c>
+      <c r="V157" s="6">
+        <v>0.055768626964191832</v>
+      </c>
+      <c r="W157" s="6">
+        <v>0.034151564051638529</v>
+      </c>
+      <c r="X157" s="8">
+        <v>30.924843396226414</v>
+      </c>
+      <c r="Y157" s="6">
+        <v>0.43396226415094341</v>
+      </c>
+      <c r="Z157" s="6">
+        <v>0.094339622641509441</v>
+      </c>
+      <c r="AA157" s="8">
+        <v>7.6462370967741942</v>
+      </c>
+      <c r="AB157" s="8">
+        <v>4.7018867924528296</v>
+      </c>
+      <c r="AC157" s="8">
+        <v>12.532074</v>
+      </c>
+      <c r="AD157" s="8">
+        <v>19.471069811320753</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>0.50943396226415094</v>
+      </c>
       <c r="AF157" s="9"/>
-      <c r="AG157" s="5"/>
+      <c r="AG157" s="5">
+        <v>0</v>
+      </c>
       <c r="AH157" s="10">
         <v>4</v>
       </c>
@@ -21317,7 +21461,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21353,25 +21497,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>6822.04</v>
+      </c>
+      <c r="P158" s="5">
+        <v>6822.04</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>0.14184045793860678</v>
+      </c>
+      <c r="R158" s="7">
+        <v>60</v>
+      </c>
+      <c r="S158" s="6">
+        <v>-0.032258064516129004</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.26258387520448428</v>
+      </c>
+      <c r="U158" s="6">
+        <v>-0.00062331795181499961</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.045810710579240223</v>
+      </c>
+      <c r="W158" s="6">
+        <v>0.014547334814806129</v>
+      </c>
+      <c r="X158" s="8">
+        <v>32.233642592592595</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>0.59259259259259256</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>5.607527419354839</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>6.317283333333334</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>11.890616</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>18.777777777777779</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.42592592592592593</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>0</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>
@@ -22178,7 +22358,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>44</v>
@@ -22214,25 +22394,61 @@
       <c t="s" r="N165" s="4">
         <v>52</v>
       </c>
-      <c r="O165" s="5"/>
-      <c r="P165" s="5"/>
-      <c r="Q165" s="6"/>
-      <c r="R165" s="7"/>
-      <c r="S165" s="6"/>
-      <c r="T165" s="6"/>
-      <c r="U165" s="6"/>
-      <c r="V165" s="6"/>
-      <c r="W165" s="6"/>
-      <c r="X165" s="8"/>
-      <c r="Y165" s="6"/>
-      <c r="Z165" s="6"/>
-      <c r="AA165" s="8"/>
-      <c r="AB165" s="8"/>
-      <c r="AC165" s="8"/>
-      <c r="AD165" s="8"/>
-      <c r="AE165" s="6"/>
+      <c r="O165" s="5">
+        <v>13727.030000000001</v>
+      </c>
+      <c r="P165" s="5">
+        <v>13727.030000000001</v>
+      </c>
+      <c r="Q165" s="6">
+        <v>0.72654447851603288</v>
+      </c>
+      <c r="R165" s="7">
+        <v>112</v>
+      </c>
+      <c r="S165" s="6">
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="T165" s="6">
+        <v>0.26010412303316888</v>
+      </c>
+      <c r="U165" s="6">
+        <v>-0.010859078766492097</v>
+      </c>
+      <c r="V165" s="6">
+        <v>0.010020157310066342</v>
+      </c>
+      <c r="W165" s="6">
+        <v>-0.004245856532694982</v>
+      </c>
+      <c r="X165" s="8">
+        <v>50.428862195121951</v>
+      </c>
+      <c r="Y165" s="6">
+        <v>0.073170731707317069</v>
+      </c>
+      <c r="Z165" s="6">
+        <v>0.64634146341463417</v>
+      </c>
+      <c r="AA165" s="8">
+        <v>13.131211818181818</v>
+      </c>
+      <c r="AB165" s="8">
+        <v>15.55223536585366</v>
+      </c>
+      <c r="AC165" s="8">
+        <v>31.203657</v>
+      </c>
+      <c r="AD165" s="8">
+        <v>38.106097560975606</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>0.15853658536585366</v>
+      </c>
       <c r="AF165" s="9"/>
-      <c r="AG165" s="5"/>
+      <c r="AG165" s="5">
+        <v>152</v>
+      </c>
       <c r="AH165" s="10">
         <v>3</v>
       </c>
